--- a/URUVS/Datasheets/URUV/09.2024/September_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/09.2024/September_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\09.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA7597C-DF3E-4070-9161-041B975E0CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7076D1-57C1-41C7-B62E-34A1C2922067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="209">
   <si>
     <t>DATE</t>
   </si>
@@ -603,6 +603,69 @@
   </si>
   <si>
     <t>30_09_2024_0853_C5_D3_TMPE3</t>
+  </si>
+  <si>
+    <t>MAXN_MUDCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STMUDCRAB</t>
+  </si>
+  <si>
+    <t>T1_MUDCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>TIME_1STSWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>T1_SWIMMERCRAB</t>
+  </si>
+  <si>
+    <t>MAXN_BIGBOI</t>
+  </si>
+  <si>
+    <t>TIME_1STBIGBOI</t>
+  </si>
+  <si>
+    <t>T1_BIGBOI</t>
+  </si>
+  <si>
+    <t>MAXN_SANDFISH</t>
+  </si>
+  <si>
+    <t>TIME_SANDFISH</t>
+  </si>
+  <si>
+    <t>T1_SANDFISH</t>
+  </si>
+  <si>
+    <t>MAXN_SHRIMP</t>
+  </si>
+  <si>
+    <t>TIME_1STSHRIMP</t>
+  </si>
+  <si>
+    <t>T1_SHRIMP</t>
+  </si>
+  <si>
+    <t>MAXN_FISHA</t>
+  </si>
+  <si>
+    <t>TIME_1STFISHA</t>
+  </si>
+  <si>
+    <t>T1_FISHA</t>
+  </si>
+  <si>
+    <t>MAXN_ULAR</t>
+  </si>
+  <si>
+    <t>TIME_1STULAR</t>
+  </si>
+  <si>
+    <t>T1_ULAR</t>
   </si>
 </sst>
 </file>
@@ -1236,14 +1299,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF2D75B-3330-44BB-BF8B-27BF0F133624}">
-  <dimension ref="A1:CW22"/>
+  <dimension ref="A1:DR22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="7" max="22" width="8.7265625" customWidth="1"/>
+    <col min="3" max="5" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.7265625" customWidth="1"/>
+    <col min="7" max="22" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="23" max="29" width="8.7265625" style="1" customWidth="1"/>
     <col min="30" max="36" width="8.7265625" customWidth="1"/>
     <col min="37" max="37" width="14.90625" bestFit="1" customWidth="1"/>
@@ -1254,14 +1317,21 @@
     <col min="52" max="52" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="8.90625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="8.90625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="100" max="100" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="103" max="103" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="109" max="109" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="112" max="112" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="118" max="118" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="121" max="121" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="122" max="122" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:101" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:122" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>147</v>
       </c>
@@ -1428,145 +1498,208 @@
         <v>38</v>
       </c>
       <c r="BD1" s="81" t="s">
+        <v>203</v>
+      </c>
+      <c r="BE1" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="BF1" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="BG1" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="BE1" s="27" t="s">
+      <c r="BH1" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="BF1" s="59" t="s">
+      <c r="BI1" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="BG1" s="81" t="s">
+      <c r="BJ1" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="BH1" s="27" t="s">
+      <c r="BK1" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="BI1" s="59" t="s">
+      <c r="BL1" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="BJ1" s="81" t="s">
+      <c r="BM1" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="BK1" s="27" t="s">
+      <c r="BN1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="BL1" s="59" t="s">
+      <c r="BO1" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="BM1" s="81" t="s">
+      <c r="BP1" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="BN1" s="27" t="s">
+      <c r="BQ1" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="BO1" s="59" t="s">
+      <c r="BR1" s="59" t="s">
         <v>61</v>
       </c>
-      <c r="BP1" s="81" t="s">
+      <c r="BS1" s="81" t="s">
         <v>62</v>
       </c>
-      <c r="BQ1" s="27" t="s">
+      <c r="BT1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="BR1" s="59" t="s">
+      <c r="BU1" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="BS1" s="81" t="s">
+      <c r="BV1" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="BT1" s="27" t="s">
+      <c r="BW1" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="BU1" s="59" t="s">
+      <c r="BX1" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="BV1" s="81" t="s">
+      <c r="BY1" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="BW1" s="27" t="s">
+      <c r="BZ1" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="BX1" s="59" t="s">
+      <c r="CA1" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="BY1" s="81" t="s">
+      <c r="CB1" s="81" t="s">
         <v>126</v>
       </c>
-      <c r="BZ1" s="27" t="s">
+      <c r="CC1" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="CA1" s="59" t="s">
+      <c r="CD1" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="CB1" s="81" t="s">
+      <c r="CE1" s="81" t="s">
         <v>138</v>
       </c>
-      <c r="CC1" s="27" t="s">
+      <c r="CF1" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="CD1" s="59" t="s">
+      <c r="CG1" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="CE1" s="81" t="s">
+      <c r="CH1" s="81" t="s">
         <v>123</v>
       </c>
-      <c r="CF1" s="27" t="s">
+      <c r="CI1" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="CG1" s="59" t="s">
+      <c r="CJ1" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="CH1" s="81" t="s">
+      <c r="CK1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="CI1" s="27" t="s">
+      <c r="CL1" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="CJ1" s="59" t="s">
+      <c r="CM1" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="CK1" s="81" t="s">
+      <c r="CN1" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="CL1" s="27" t="s">
+      <c r="CO1" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="CM1" s="59" t="s">
+      <c r="CP1" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="CN1" s="81" t="s">
+      <c r="CQ1" s="81" t="s">
         <v>65</v>
       </c>
-      <c r="CO1" s="27" t="s">
+      <c r="CR1" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="CP1" s="59" t="s">
+      <c r="CS1" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="CQ1" s="81" t="s">
+      <c r="CT1" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="CR1" s="27" t="s">
+      <c r="CU1" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="CS1" s="59" t="s">
+      <c r="CV1" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="CT1" s="81" t="s">
+      <c r="CW1" s="81" t="s">
+        <v>194</v>
+      </c>
+      <c r="CX1" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="CY1" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="CZ1" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="DA1" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="DB1" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="DC1" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="CU1" s="27" t="s">
+      <c r="DD1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="CV1" s="59" t="s">
+      <c r="DE1" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="CW1" s="28" t="s">
+      <c r="DF1" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="DG1" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="DH1" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="DI1" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="DJ1" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="DK1" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="DL1" s="81" t="s">
+        <v>200</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="DN1" s="59" t="s">
+        <v>202</v>
+      </c>
+      <c r="DO1" s="81" t="s">
+        <v>206</v>
+      </c>
+      <c r="DP1" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="DQ1" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="DR1" s="28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>149</v>
       </c>
@@ -1635,32 +1768,52 @@
         <v>156</v>
       </c>
       <c r="V2" s="8"/>
-      <c r="W2" s="19"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
+      <c r="W2" s="19">
+        <v>2.5405092592592594E-2</v>
+      </c>
+      <c r="X2" s="20">
+        <v>1.8020833333333333E-2</v>
+      </c>
+      <c r="Y2" s="20">
+        <v>5.6712962962962967E-3</v>
+      </c>
       <c r="Z2" s="20"/>
       <c r="AA2" s="20"/>
       <c r="AB2" s="20"/>
       <c r="AC2" s="20">
         <f>SUM(W2:AB2)</f>
-        <v>0</v>
-      </c>
-      <c r="AD2" s="20"/>
+        <v>4.9097222222222223E-2</v>
+      </c>
+      <c r="AD2" s="20">
+        <v>3.9004629629629628E-3</v>
+      </c>
       <c r="AE2" s="20"/>
       <c r="AF2" s="20">
         <f t="shared" ref="AF2:AF13" si="0">AC2-AD2-AE2</f>
+        <v>4.5196759259259263E-2</v>
+      </c>
+      <c r="AG2" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH2" s="21">
+        <v>95</v>
+      </c>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="29">
+        <v>4</v>
+      </c>
+      <c r="AK2" s="30">
+        <v>2</v>
+      </c>
+      <c r="AL2" s="31">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="34">
+        <v>3.9004629629629628E-3</v>
+      </c>
+      <c r="AN2" s="33">
+        <f t="shared" ref="AN2:AN13" si="1">IF(AL2=0,"NA",AM2-$AD2)</f>
         <v>0</v>
-      </c>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="29"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="33" t="str">
-        <f t="shared" ref="AN2:AN13" si="1">IF(AL2=0,"NA",AM2-$AD2)</f>
-        <v>NA</v>
       </c>
       <c r="AO2" s="31"/>
       <c r="AP2" s="56"/>
@@ -1695,7 +1848,7 @@
       <c r="BD2" s="58"/>
       <c r="BE2" s="57"/>
       <c r="BF2" s="33" t="str">
-        <f t="shared" ref="BF2:BF13" si="7">IF(BD2=0,"NA",BE2-$AD2)</f>
+        <f t="shared" ref="BF2:BF22" si="7">IF(BD2=0,"NA",BE2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="BG2" s="58"/>
@@ -1723,68 +1876,126 @@
         <v>NA</v>
       </c>
       <c r="BS2" s="58"/>
-      <c r="BT2" s="72"/>
+      <c r="BT2" s="57"/>
       <c r="BU2" s="33" t="str">
         <f t="shared" ref="BU2:BU13" si="12">IF(BS2=0,"NA",BT2-$AD2)</f>
         <v>NA</v>
       </c>
-      <c r="BV2" s="58"/>
-      <c r="BW2" s="57"/>
-      <c r="BX2" s="33" t="str">
-        <f t="shared" ref="BX2:BX22" si="13">IF(BV2=0,"NA",BW2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="BY2" s="31"/>
-      <c r="BZ2" s="56"/>
+      <c r="BV2" s="58">
+        <v>1</v>
+      </c>
+      <c r="BW2" s="72">
+        <v>4.71875E-2</v>
+      </c>
+      <c r="BX2" s="33">
+        <f>IF(BV2=0,"NA",BW2-$AD2)</f>
+        <v>4.3287037037037041E-2</v>
+      </c>
+      <c r="BY2" s="58"/>
+      <c r="BZ2" s="57"/>
       <c r="CA2" s="33" t="str">
-        <f t="shared" ref="CA2:CA22" si="14">IF(BY2=0,"NA",BZ2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="CB2" s="58"/>
-      <c r="CC2" s="71"/>
+        <f t="shared" ref="CA2:CA22" si="13">IF(BY2=0,"NA",BZ2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="CB2" s="31"/>
+      <c r="CC2" s="56"/>
       <c r="CD2" s="33" t="str">
-        <f t="shared" ref="CD2:CD22" si="15">IF(CB2=0,"NA",CC2-$AD2)</f>
+        <f t="shared" ref="CD2:CD22" si="14">IF(CB2=0,"NA",CC2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CE2" s="58"/>
       <c r="CF2" s="71"/>
       <c r="CG2" s="33" t="str">
-        <f t="shared" ref="CG2:CG22" si="16">IF(CE2=0,"NA",CF2-$AD2)</f>
+        <f t="shared" ref="CG2:CG22" si="15">IF(CE2=0,"NA",CF2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CH2" s="58"/>
       <c r="CI2" s="71"/>
       <c r="CJ2" s="33" t="str">
-        <f t="shared" ref="CJ2:CJ22" si="17">IF(CH2=0,"NA",CI2-$AD2)</f>
+        <f t="shared" ref="CJ2:CJ22" si="16">IF(CH2=0,"NA",CI2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CK2" s="58"/>
       <c r="CL2" s="71"/>
       <c r="CM2" s="33" t="str">
-        <f t="shared" ref="CM2:CM22" si="18">IF(CK2=0,"NA",CL2-$AD2)</f>
+        <f t="shared" ref="CM2:CM22" si="17">IF(CK2=0,"NA",CL2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CN2" s="58"/>
       <c r="CO2" s="71"/>
       <c r="CP2" s="33" t="str">
-        <f t="shared" ref="CP2:CP22" si="19">IF(CN2=0,"NA",CO2-$AD2)</f>
+        <f t="shared" ref="CP2:CP22" si="18">IF(CN2=0,"NA",CO2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CQ2" s="58"/>
       <c r="CR2" s="71"/>
       <c r="CS2" s="33" t="str">
-        <f t="shared" ref="CS2:CS22" si="20">IF(CQ2=0,"NA",CR2-$AD2)</f>
+        <f t="shared" ref="CS2:CS22" si="19">IF(CQ2=0,"NA",CR2-$AD2)</f>
         <v>NA</v>
       </c>
       <c r="CT2" s="58"/>
       <c r="CU2" s="71"/>
       <c r="CV2" s="33" t="str">
-        <f t="shared" ref="CV2:CV13" si="21">IF(CT2=0,"NA",CU2-$AD2)</f>
-        <v>NA</v>
-      </c>
-      <c r="CW2" s="35"/>
+        <f t="shared" ref="CV2:CV22" si="20">IF(CT2=0,"NA",CU2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="CW2" s="58"/>
+      <c r="CX2" s="71"/>
+      <c r="CY2" s="33" t="str">
+        <f t="shared" ref="CY2:CY22" si="21">IF(CW2=0,"NA",CX2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="CZ2" s="58"/>
+      <c r="DA2" s="71"/>
+      <c r="DB2" s="33" t="str">
+        <f t="shared" ref="DB2:DB22" si="22">IF(CZ2=0,"NA",DA2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DC2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DD2" s="71">
+        <v>9.2476851851851852E-3</v>
+      </c>
+      <c r="DE2" s="33">
+        <f t="shared" ref="DE2:DE13" si="23">IF(DC2=0,"NA",DD2-$AD2)</f>
+        <v>5.347222222222222E-3</v>
+      </c>
+      <c r="DF2" s="58">
+        <v>3</v>
+      </c>
+      <c r="DG2" s="71">
+        <v>4.0856481481481481E-3</v>
+      </c>
+      <c r="DH2" s="33">
+        <f t="shared" ref="DH2:DH22" si="24">IF(DF2=0,"NA",DG2-$AD2)</f>
+        <v>1.8518518518518537E-4</v>
+      </c>
+      <c r="DI2" s="58">
+        <v>1</v>
+      </c>
+      <c r="DJ2" s="71">
+        <v>4.9722222222222223E-2</v>
+      </c>
+      <c r="DK2" s="33">
+        <f t="shared" ref="DK2:DK22" si="25">IF(DI2=0,"NA",DJ2-$AD2)</f>
+        <v>4.5821759259259263E-2</v>
+      </c>
+      <c r="DL2" s="58"/>
+      <c r="DM2" s="71"/>
+      <c r="DN2" s="33" t="str">
+        <f t="shared" ref="DN2:DN22" si="26">IF(DL2=0,"NA",DM2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DO2" s="58"/>
+      <c r="DP2" s="71"/>
+      <c r="DQ2" s="33" t="str">
+        <f t="shared" ref="DQ2:DQ22" si="27">IF(DO2=0,"NA",DP2-$AD2)</f>
+        <v>NA</v>
+      </c>
+      <c r="DR2" s="35"/>
     </row>
-    <row r="3" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>149</v>
       </c>
@@ -1801,7 +2012,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="74" t="str">
-        <f t="shared" ref="F3:F22" si="22">D3&amp;""&amp;E3</f>
+        <f t="shared" ref="F3:F22" si="28">D3&amp;""&amp;E3</f>
         <v>E6</v>
       </c>
       <c r="G3" s="5">
@@ -1837,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q22" si="23">J3-I3</f>
+        <f t="shared" ref="Q3:Q22" si="29">J3-I3</f>
         <v>0.10069444444444442</v>
       </c>
       <c r="R3" s="6" t="s">
@@ -1853,27 +2064,47 @@
         <v>156</v>
       </c>
       <c r="V3" s="8"/>
-      <c r="W3" s="19"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
+      <c r="W3" s="19">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="X3" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="Y3" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>8.773148148148148E-3</v>
+      </c>
       <c r="AA3" s="20"/>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20">
-        <f t="shared" ref="AC3:AC22" si="24">SUM(W3:AB3)</f>
-        <v>0</v>
-      </c>
-      <c r="AD3" s="20"/>
-      <c r="AE3" s="20"/>
+        <f t="shared" ref="AC3:AC22" si="30">SUM(W3:AB3)</f>
+        <v>5.3356481481481484E-2</v>
+      </c>
+      <c r="AD3" s="20">
+        <v>4.3287037037037035E-3</v>
+      </c>
+      <c r="AE3" s="20">
+        <v>6.9444444444444441E-3</v>
+      </c>
       <c r="AF3" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG3" s="21"/>
-      <c r="AH3" s="21"/>
+        <v>4.2083333333333334E-2</v>
+      </c>
+      <c r="AG3" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH3" s="21">
+        <v>70</v>
+      </c>
       <c r="AI3" s="22"/>
-      <c r="AJ3" s="29"/>
-      <c r="AK3" s="30"/>
+      <c r="AJ3" s="29">
+        <v>7</v>
+      </c>
+      <c r="AK3" s="30">
+        <v>7</v>
+      </c>
       <c r="AL3" s="31"/>
       <c r="AM3" s="34"/>
       <c r="AN3" s="33" t="str">
@@ -1886,11 +2117,15 @@
         <f t="shared" si="2"/>
         <v>NA</v>
       </c>
-      <c r="AR3" s="31"/>
-      <c r="AS3" s="32"/>
-      <c r="AT3" s="33" t="str">
+      <c r="AR3" s="31">
+        <v>23</v>
+      </c>
+      <c r="AS3" s="34">
+        <v>4.4675925925925924E-3</v>
+      </c>
+      <c r="AT3" s="33">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>1.3888888888888892E-4</v>
       </c>
       <c r="AU3" s="31"/>
       <c r="AV3" s="32"/>
@@ -1904,11 +2139,15 @@
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA3" s="31"/>
-      <c r="BB3" s="32"/>
-      <c r="BC3" s="33" t="str">
+      <c r="BA3" s="31">
+        <v>1</v>
+      </c>
+      <c r="BB3" s="34">
+        <v>9.6874999999999999E-3</v>
+      </c>
+      <c r="BC3" s="33">
         <f t="shared" si="6"/>
-        <v>NA</v>
+        <v>5.3587962962962964E-3</v>
       </c>
       <c r="BD3" s="31"/>
       <c r="BE3" s="32"/>
@@ -1928,11 +2167,15 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM3" s="31"/>
-      <c r="BN3" s="32"/>
-      <c r="BO3" s="33" t="str">
+      <c r="BM3" s="31">
+        <v>19</v>
+      </c>
+      <c r="BN3" s="34">
+        <v>1.5752314814814816E-2</v>
+      </c>
+      <c r="BO3" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>1.1423611111111114E-2</v>
       </c>
       <c r="BP3" s="31"/>
       <c r="BQ3" s="32"/>
@@ -1946,63 +2189,121 @@
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
-      <c r="BV3" s="31"/>
-      <c r="BW3" s="32"/>
-      <c r="BX3" s="33" t="str">
+      <c r="BV3" s="31">
+        <v>5</v>
+      </c>
+      <c r="BW3" s="34">
+        <v>1.6898148148148148E-2</v>
+      </c>
+      <c r="BX3" s="33">
+        <f t="shared" ref="BX3:BX13" si="31">IF(BV3=0,"NA",BW3-$AD3)</f>
+        <v>1.2569444444444446E-2</v>
+      </c>
+      <c r="BY3" s="31"/>
+      <c r="BZ3" s="32"/>
+      <c r="CA3" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY3" s="31"/>
-      <c r="BZ3" s="56"/>
-      <c r="CA3" s="33" t="str">
+      <c r="CB3" s="31"/>
+      <c r="CC3" s="56"/>
+      <c r="CD3" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB3" s="31"/>
-      <c r="CC3" s="32"/>
-      <c r="CD3" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE3" s="31"/>
       <c r="CF3" s="32"/>
       <c r="CG3" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH3" s="31"/>
       <c r="CI3" s="32"/>
       <c r="CJ3" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK3" s="31"/>
       <c r="CL3" s="32"/>
       <c r="CM3" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN3" s="31"/>
       <c r="CO3" s="32"/>
       <c r="CP3" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ3" s="31"/>
       <c r="CR3" s="32"/>
       <c r="CS3" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT3" s="31"/>
       <c r="CU3" s="32"/>
       <c r="CV3" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW3" s="31">
+        <v>1</v>
+      </c>
+      <c r="CX3" s="34">
+        <v>4.43287037037037E-3</v>
+      </c>
+      <c r="CY3" s="33">
         <f t="shared" si="21"/>
-        <v>NA</v>
-      </c>
-      <c r="CW3" s="35"/>
+        <v>1.0416666666666647E-4</v>
+      </c>
+      <c r="CZ3" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA3" s="34">
+        <v>1.758101851851852E-2</v>
+      </c>
+      <c r="DB3" s="33">
+        <f t="shared" si="22"/>
+        <v>1.3252314814814817E-2</v>
+      </c>
+      <c r="DC3" s="31">
+        <v>3</v>
+      </c>
+      <c r="DD3" s="34">
+        <v>6.1805555555555555E-3</v>
+      </c>
+      <c r="DE3" s="33">
+        <f t="shared" si="23"/>
+        <v>1.8518518518518519E-3</v>
+      </c>
+      <c r="DF3" s="31"/>
+      <c r="DG3" s="32"/>
+      <c r="DH3" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI3" s="31"/>
+      <c r="DJ3" s="32"/>
+      <c r="DK3" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL3" s="31"/>
+      <c r="DM3" s="32"/>
+      <c r="DN3" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO3" s="31"/>
+      <c r="DP3" s="32"/>
+      <c r="DQ3" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR3" s="35"/>
     </row>
-    <row r="4" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>149</v>
       </c>
@@ -2019,7 +2320,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>E4</v>
       </c>
       <c r="G4" s="5">
@@ -2055,7 +2356,7 @@
         <v>3</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>9.4444444444444442E-2</v>
       </c>
       <c r="R4" s="6" t="s">
@@ -2071,27 +2372,43 @@
         <v>156</v>
       </c>
       <c r="V4" s="8"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
+      <c r="W4" s="19">
+        <v>1.8680555555555554E-2</v>
+      </c>
+      <c r="X4" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y4" s="20">
+        <v>1.2615740740740742E-2</v>
+      </c>
       <c r="Z4" s="20"/>
       <c r="AA4" s="20"/>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD4" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.9155092592592591E-2</v>
+      </c>
+      <c r="AD4" s="20">
+        <v>3.9120370370370368E-3</v>
+      </c>
       <c r="AE4" s="20"/>
       <c r="AF4" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG4" s="21"/>
-      <c r="AH4" s="21"/>
+        <v>4.524305555555555E-2</v>
+      </c>
+      <c r="AG4" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH4" s="21">
+        <v>70</v>
+      </c>
       <c r="AI4" s="22"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="30"/>
+      <c r="AJ4" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="30">
+        <v>4</v>
+      </c>
       <c r="AL4" s="31"/>
       <c r="AM4" s="34"/>
       <c r="AN4" s="33" t="str">
@@ -2104,11 +2421,15 @@
         <f t="shared" si="2"/>
         <v>NA</v>
       </c>
-      <c r="AR4" s="31"/>
-      <c r="AS4" s="32"/>
-      <c r="AT4" s="33" t="str">
+      <c r="AR4" s="31">
+        <v>29</v>
+      </c>
+      <c r="AS4" s="34">
+        <v>4.2245370370370371E-3</v>
+      </c>
+      <c r="AT4" s="33">
         <f t="shared" si="3"/>
-        <v>NA</v>
+        <v>3.1250000000000028E-4</v>
       </c>
       <c r="AU4" s="31"/>
       <c r="AV4" s="32"/>
@@ -2135,7 +2456,7 @@
         <v>NA</v>
       </c>
       <c r="BG4" s="31"/>
-      <c r="BH4" s="34"/>
+      <c r="BH4" s="32"/>
       <c r="BI4" s="33" t="str">
         <f t="shared" si="8"/>
         <v>NA</v>
@@ -2146,11 +2467,15 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM4" s="31"/>
-      <c r="BN4" s="32"/>
-      <c r="BO4" s="33" t="str">
+      <c r="BM4" s="31">
+        <v>8</v>
+      </c>
+      <c r="BN4" s="34">
+        <v>1.1226851851851852E-2</v>
+      </c>
+      <c r="BO4" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>7.3148148148148157E-3</v>
       </c>
       <c r="BP4" s="31"/>
       <c r="BQ4" s="32"/>
@@ -2167,60 +2492,114 @@
       <c r="BV4" s="31"/>
       <c r="BW4" s="32"/>
       <c r="BX4" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY4" s="31"/>
+      <c r="BZ4" s="32"/>
+      <c r="CA4" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY4" s="31"/>
-      <c r="BZ4" s="56"/>
-      <c r="CA4" s="33" t="str">
+      <c r="CB4" s="31"/>
+      <c r="CC4" s="56"/>
+      <c r="CD4" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB4" s="31"/>
-      <c r="CC4" s="34"/>
-      <c r="CD4" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE4" s="31"/>
       <c r="CF4" s="34"/>
       <c r="CG4" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH4" s="31"/>
       <c r="CI4" s="34"/>
       <c r="CJ4" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK4" s="31"/>
       <c r="CL4" s="34"/>
       <c r="CM4" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN4" s="31"/>
       <c r="CO4" s="34"/>
       <c r="CP4" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ4" s="31"/>
       <c r="CR4" s="34"/>
       <c r="CS4" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT4" s="31"/>
       <c r="CU4" s="34"/>
       <c r="CV4" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW4" s="31"/>
+      <c r="CX4" s="34"/>
+      <c r="CY4" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW4" s="35"/>
+      <c r="CZ4" s="31">
+        <v>2</v>
+      </c>
+      <c r="DA4" s="34">
+        <v>3.4097222222222223E-2</v>
+      </c>
+      <c r="DB4" s="33">
+        <f t="shared" si="22"/>
+        <v>3.0185185185185186E-2</v>
+      </c>
+      <c r="DC4" s="31">
+        <v>1</v>
+      </c>
+      <c r="DD4" s="34">
+        <v>8.7615740740740744E-3</v>
+      </c>
+      <c r="DE4" s="33">
+        <f t="shared" si="23"/>
+        <v>4.8495370370370376E-3</v>
+      </c>
+      <c r="DF4" s="31">
+        <v>3</v>
+      </c>
+      <c r="DG4" s="34">
+        <v>6.5624999999999998E-3</v>
+      </c>
+      <c r="DH4" s="33">
+        <f t="shared" si="24"/>
+        <v>2.650462962962963E-3</v>
+      </c>
+      <c r="DI4" s="31"/>
+      <c r="DJ4" s="34"/>
+      <c r="DK4" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL4" s="31"/>
+      <c r="DM4" s="34"/>
+      <c r="DN4" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO4" s="31"/>
+      <c r="DP4" s="34"/>
+      <c r="DQ4" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR4" s="35"/>
     </row>
-    <row r="5" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>149</v>
       </c>
@@ -2237,7 +2616,7 @@
         <v>4</v>
       </c>
       <c r="F5" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L4</v>
       </c>
       <c r="G5" s="5">
@@ -2273,7 +2652,7 @@
         <v>3</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.2083333333333315E-2</v>
       </c>
       <c r="R5" s="6" t="s">
@@ -2289,38 +2668,58 @@
         <v>156</v>
       </c>
       <c r="V5" s="8"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
+      <c r="W5" s="19">
+        <v>2.2743055555555555E-2</v>
+      </c>
+      <c r="X5" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>2.9745370370370373E-3</v>
+      </c>
       <c r="Z5" s="20"/>
       <c r="AA5" s="20"/>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD5" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.3576388888888887E-2</v>
+      </c>
+      <c r="AD5" s="20">
+        <v>4.3750000000000004E-3</v>
+      </c>
       <c r="AE5" s="20"/>
       <c r="AF5" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG5" s="21"/>
-      <c r="AH5" s="21"/>
+        <v>3.9201388888888883E-2</v>
+      </c>
+      <c r="AG5" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH5" s="21">
+        <v>100</v>
+      </c>
       <c r="AI5" s="22"/>
-      <c r="AJ5" s="29"/>
-      <c r="AK5" s="30"/>
+      <c r="AJ5" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK5" s="30">
+        <v>4</v>
+      </c>
       <c r="AL5" s="31"/>
       <c r="AM5" s="34"/>
       <c r="AN5" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO5" s="31"/>
-      <c r="AP5" s="32"/>
-      <c r="AQ5" s="33" t="str">
+      <c r="AO5" s="31">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="34">
+        <v>6.7129629629629631E-3</v>
+      </c>
+      <c r="AQ5" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>2.3379629629629627E-3</v>
       </c>
       <c r="AR5" s="31"/>
       <c r="AS5" s="32"/>
@@ -2364,11 +2763,15 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM5" s="31"/>
-      <c r="BN5" s="32"/>
-      <c r="BO5" s="33" t="str">
+      <c r="BM5" s="31">
+        <v>1</v>
+      </c>
+      <c r="BN5" s="34">
+        <v>1.7476851851851851E-2</v>
+      </c>
+      <c r="BO5" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>1.3101851851851851E-2</v>
       </c>
       <c r="BP5" s="31"/>
       <c r="BQ5" s="32"/>
@@ -2385,60 +2788,114 @@
       <c r="BV5" s="31"/>
       <c r="BW5" s="32"/>
       <c r="BX5" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY5" s="31"/>
+      <c r="BZ5" s="32"/>
+      <c r="CA5" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY5" s="31"/>
-      <c r="BZ5" s="56"/>
-      <c r="CA5" s="33" t="str">
+      <c r="CB5" s="31"/>
+      <c r="CC5" s="56"/>
+      <c r="CD5" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB5" s="31"/>
-      <c r="CC5" s="32"/>
-      <c r="CD5" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE5" s="31"/>
       <c r="CF5" s="32"/>
       <c r="CG5" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH5" s="31"/>
       <c r="CI5" s="32"/>
       <c r="CJ5" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK5" s="31"/>
       <c r="CL5" s="32"/>
       <c r="CM5" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN5" s="31"/>
       <c r="CO5" s="32"/>
       <c r="CP5" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ5" s="31"/>
       <c r="CR5" s="32"/>
       <c r="CS5" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT5" s="31"/>
       <c r="CU5" s="32"/>
       <c r="CV5" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW5" s="31"/>
+      <c r="CX5" s="32"/>
+      <c r="CY5" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW5" s="35"/>
+      <c r="CZ5" s="31">
+        <v>3</v>
+      </c>
+      <c r="DA5" s="34">
+        <v>6.5162037037037037E-3</v>
+      </c>
+      <c r="DB5" s="33">
+        <f t="shared" si="22"/>
+        <v>2.1412037037037033E-3</v>
+      </c>
+      <c r="DC5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DD5" s="34">
+        <v>2.0555555555555556E-2</v>
+      </c>
+      <c r="DE5" s="33">
+        <f t="shared" si="23"/>
+        <v>1.6180555555555556E-2</v>
+      </c>
+      <c r="DF5" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG5" s="34">
+        <v>8.5995370370370375E-3</v>
+      </c>
+      <c r="DH5" s="33">
+        <f t="shared" si="24"/>
+        <v>4.2245370370370371E-3</v>
+      </c>
+      <c r="DI5" s="31"/>
+      <c r="DJ5" s="32"/>
+      <c r="DK5" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL5" s="31"/>
+      <c r="DM5" s="32"/>
+      <c r="DN5" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO5" s="31"/>
+      <c r="DP5" s="32"/>
+      <c r="DQ5" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR5" s="35"/>
     </row>
-    <row r="6" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>149</v>
       </c>
@@ -2455,7 +2912,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D5</v>
       </c>
       <c r="G6" s="5">
@@ -2491,7 +2948,7 @@
         <v>3</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>8.4027777777777812E-2</v>
       </c>
       <c r="R6" s="6" t="s">
@@ -2507,27 +2964,43 @@
         <v>165</v>
       </c>
       <c r="V6" s="8"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
+      <c r="W6" s="19">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="X6" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>1.0358796296296297E-2</v>
+      </c>
       <c r="Z6" s="20"/>
       <c r="AA6" s="20"/>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD6" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.6076388888888889E-2</v>
+      </c>
+      <c r="AD6" s="20">
+        <v>3.8194444444444443E-3</v>
+      </c>
       <c r="AE6" s="20"/>
       <c r="AF6" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG6" s="21"/>
-      <c r="AH6" s="21"/>
+        <v>4.2256944444444444E-2</v>
+      </c>
+      <c r="AG6" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH6" s="21">
+        <v>95</v>
+      </c>
       <c r="AI6" s="22"/>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="30"/>
+      <c r="AJ6" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="30">
+        <v>3</v>
+      </c>
       <c r="AL6" s="31"/>
       <c r="AM6" s="34"/>
       <c r="AN6" s="33" t="str">
@@ -2558,11 +3031,15 @@
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA6" s="31"/>
-      <c r="BB6" s="32"/>
-      <c r="BC6" s="33" t="str">
+      <c r="BA6" s="31">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="34">
+        <v>7.9861111111111105E-3</v>
+      </c>
+      <c r="BC6" s="33">
         <f t="shared" si="6"/>
-        <v>NA</v>
+        <v>4.1666666666666657E-3</v>
       </c>
       <c r="BD6" s="31"/>
       <c r="BE6" s="32"/>
@@ -2603,60 +3080,118 @@
       <c r="BV6" s="31"/>
       <c r="BW6" s="32"/>
       <c r="BX6" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY6" s="31"/>
+      <c r="BZ6" s="32"/>
+      <c r="CA6" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY6" s="31"/>
-      <c r="BZ6" s="56"/>
-      <c r="CA6" s="33" t="str">
+      <c r="CB6" s="31"/>
+      <c r="CC6" s="56"/>
+      <c r="CD6" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB6" s="31"/>
-      <c r="CC6" s="32"/>
-      <c r="CD6" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE6" s="31"/>
       <c r="CF6" s="32"/>
       <c r="CG6" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH6" s="31"/>
       <c r="CI6" s="32"/>
       <c r="CJ6" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK6" s="31"/>
       <c r="CL6" s="32"/>
       <c r="CM6" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN6" s="31"/>
       <c r="CO6" s="32"/>
       <c r="CP6" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ6" s="31"/>
       <c r="CR6" s="32"/>
       <c r="CS6" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT6" s="31"/>
       <c r="CU6" s="32"/>
       <c r="CV6" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW6" s="31">
+        <v>1</v>
+      </c>
+      <c r="CX6" s="34">
+        <v>1.6053240740740739E-2</v>
+      </c>
+      <c r="CY6" s="33">
         <f t="shared" si="21"/>
-        <v>NA</v>
-      </c>
-      <c r="CW6" s="35"/>
+        <v>1.2233796296296295E-2</v>
+      </c>
+      <c r="CZ6" s="31"/>
+      <c r="DA6" s="32"/>
+      <c r="DB6" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DD6" s="34">
+        <v>1.2824074074074075E-2</v>
+      </c>
+      <c r="DE6" s="33">
+        <f t="shared" si="23"/>
+        <v>9.0046296296296298E-3</v>
+      </c>
+      <c r="DF6" s="31">
+        <v>2</v>
+      </c>
+      <c r="DG6" s="34">
+        <v>1.9270833333333334E-2</v>
+      </c>
+      <c r="DH6" s="33">
+        <f t="shared" si="24"/>
+        <v>1.545138888888889E-2</v>
+      </c>
+      <c r="DI6" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ6" s="34">
+        <v>3.6319444444444446E-2</v>
+      </c>
+      <c r="DK6" s="33">
+        <f t="shared" si="25"/>
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="DL6" s="31"/>
+      <c r="DM6" s="34"/>
+      <c r="DN6" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO6" s="31"/>
+      <c r="DP6" s="34"/>
+      <c r="DQ6" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR6" s="35"/>
     </row>
-    <row r="7" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>149</v>
       </c>
@@ -2673,7 +3208,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D6</v>
       </c>
       <c r="G7" s="5">
@@ -2709,7 +3244,7 @@
         <v>3</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.2777777777777812E-2</v>
       </c>
       <c r="R7" s="6" t="s">
@@ -2725,38 +3260,58 @@
         <v>156</v>
       </c>
       <c r="V7" s="8"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
+      <c r="W7" s="19">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="X7" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y7" s="20">
+        <v>4.409722222222222E-3</v>
+      </c>
       <c r="Z7" s="20"/>
       <c r="AA7" s="20"/>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD7" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.0127314814814817E-2</v>
+      </c>
+      <c r="AD7" s="20">
+        <v>3.8194444444444443E-3</v>
+      </c>
       <c r="AE7" s="20"/>
       <c r="AF7" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG7" s="21"/>
-      <c r="AH7" s="21"/>
+        <v>3.6307870370370372E-2</v>
+      </c>
+      <c r="AG7" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH7" s="21">
+        <v>95</v>
+      </c>
       <c r="AI7" s="22"/>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="30"/>
+      <c r="AJ7" s="29">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="30">
+        <v>3</v>
+      </c>
       <c r="AL7" s="31"/>
       <c r="AM7" s="34"/>
       <c r="AN7" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO7" s="31"/>
-      <c r="AP7" s="32"/>
-      <c r="AQ7" s="33" t="str">
+      <c r="AO7" s="31">
+        <v>1</v>
+      </c>
+      <c r="AP7" s="34">
+        <v>1.3993055555555555E-2</v>
+      </c>
+      <c r="AQ7" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>1.0173611111111111E-2</v>
       </c>
       <c r="AR7" s="31"/>
       <c r="AS7" s="32"/>
@@ -2776,11 +3331,15 @@
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA7" s="31"/>
-      <c r="BB7" s="32"/>
-      <c r="BC7" s="33" t="str">
+      <c r="BA7" s="31">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="34">
+        <v>1.1076388888888889E-2</v>
+      </c>
+      <c r="BC7" s="33">
         <f t="shared" si="6"/>
-        <v>NA</v>
+        <v>7.2569444444444443E-3</v>
       </c>
       <c r="BD7" s="31"/>
       <c r="BE7" s="32"/>
@@ -2821,60 +3380,110 @@
       <c r="BV7" s="31"/>
       <c r="BW7" s="32"/>
       <c r="BX7" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY7" s="31"/>
+      <c r="BZ7" s="32"/>
+      <c r="CA7" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY7" s="31"/>
-      <c r="BZ7" s="56"/>
-      <c r="CA7" s="33" t="str">
+      <c r="CB7" s="31"/>
+      <c r="CC7" s="56"/>
+      <c r="CD7" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB7" s="31"/>
-      <c r="CC7" s="32"/>
-      <c r="CD7" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE7" s="31"/>
       <c r="CF7" s="32"/>
       <c r="CG7" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH7" s="31"/>
       <c r="CI7" s="32"/>
       <c r="CJ7" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK7" s="31"/>
       <c r="CL7" s="32"/>
       <c r="CM7" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN7" s="31"/>
       <c r="CO7" s="32"/>
       <c r="CP7" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ7" s="31"/>
       <c r="CR7" s="32"/>
       <c r="CS7" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT7" s="31"/>
       <c r="CU7" s="32"/>
       <c r="CV7" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW7" s="31"/>
+      <c r="CX7" s="32"/>
+      <c r="CY7" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW7" s="35"/>
+      <c r="CZ7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA7" s="34">
+        <v>1.6597222222222222E-2</v>
+      </c>
+      <c r="DB7" s="33">
+        <f t="shared" si="22"/>
+        <v>1.2777777777777777E-2</v>
+      </c>
+      <c r="DC7" s="31"/>
+      <c r="DD7" s="32"/>
+      <c r="DE7" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DF7" s="31">
+        <v>1</v>
+      </c>
+      <c r="DG7" s="34">
+        <v>5.2430555555555555E-3</v>
+      </c>
+      <c r="DH7" s="33">
+        <f t="shared" si="24"/>
+        <v>1.4236111111111112E-3</v>
+      </c>
+      <c r="DI7" s="31"/>
+      <c r="DJ7" s="32"/>
+      <c r="DK7" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL7" s="31"/>
+      <c r="DM7" s="32"/>
+      <c r="DN7" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO7" s="31"/>
+      <c r="DP7" s="32"/>
+      <c r="DQ7" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR7" s="35"/>
     </row>
-    <row r="8" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>149</v>
       </c>
@@ -2891,7 +3500,7 @@
         <v>4</v>
       </c>
       <c r="F8" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D4</v>
       </c>
       <c r="G8" s="5">
@@ -2927,7 +3536,7 @@
         <v>4</v>
       </c>
       <c r="Q8" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>7.0138888888888917E-2</v>
       </c>
       <c r="R8" s="6" t="s">
@@ -2943,27 +3552,45 @@
         <v>165</v>
       </c>
       <c r="V8" s="8"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
-      <c r="Z8" s="20"/>
+      <c r="W8" s="19">
+        <v>1.9143518518518518E-2</v>
+      </c>
+      <c r="X8" s="20">
+        <v>1.9872685185185184E-2</v>
+      </c>
+      <c r="Y8" s="20">
+        <v>1.800925925925926E-2</v>
+      </c>
+      <c r="Z8" s="20">
+        <v>3.4722222222222224E-4</v>
+      </c>
       <c r="AA8" s="20"/>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD8" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.7372685185185186E-2</v>
+      </c>
+      <c r="AD8" s="20">
+        <v>7.9861111111111105E-3</v>
+      </c>
       <c r="AE8" s="20"/>
       <c r="AF8" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG8" s="21"/>
-      <c r="AH8" s="21"/>
+        <v>4.9386574074074076E-2</v>
+      </c>
+      <c r="AG8" s="21">
+        <v>90</v>
+      </c>
+      <c r="AH8" s="21">
+        <v>95</v>
+      </c>
       <c r="AI8" s="22"/>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="30"/>
+      <c r="AJ8" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK8" s="30">
+        <v>3</v>
+      </c>
       <c r="AL8" s="31"/>
       <c r="AM8" s="34"/>
       <c r="AN8" s="33" t="str">
@@ -3018,11 +3645,15 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM8" s="31"/>
-      <c r="BN8" s="32"/>
-      <c r="BO8" s="33" t="str">
+      <c r="BM8" s="31">
+        <v>2</v>
+      </c>
+      <c r="BN8" s="34">
+        <v>1.0648148148148148E-2</v>
+      </c>
+      <c r="BO8" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>2.6620370370370374E-3</v>
       </c>
       <c r="BP8" s="31"/>
       <c r="BQ8" s="32"/>
@@ -3039,60 +3670,118 @@
       <c r="BV8" s="31"/>
       <c r="BW8" s="32"/>
       <c r="BX8" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY8" s="31"/>
+      <c r="BZ8" s="32"/>
+      <c r="CA8" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY8" s="31"/>
-      <c r="BZ8" s="56"/>
-      <c r="CA8" s="33" t="str">
+      <c r="CB8" s="31"/>
+      <c r="CC8" s="56"/>
+      <c r="CD8" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB8" s="31"/>
-      <c r="CC8" s="32"/>
-      <c r="CD8" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE8" s="31"/>
       <c r="CF8" s="32"/>
       <c r="CG8" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH8" s="31"/>
       <c r="CI8" s="32"/>
       <c r="CJ8" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK8" s="31"/>
       <c r="CL8" s="32"/>
       <c r="CM8" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN8" s="31"/>
       <c r="CO8" s="32"/>
       <c r="CP8" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ8" s="31"/>
+      <c r="CR8" s="32"/>
+      <c r="CS8" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="CQ8" s="31"/>
-      <c r="CR8" s="70"/>
-      <c r="CS8" s="33" t="str">
-        <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT8" s="31"/>
       <c r="CU8" s="70"/>
       <c r="CV8" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW8" s="31"/>
+      <c r="CX8" s="70"/>
+      <c r="CY8" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW8" s="35"/>
+      <c r="CZ8" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA8" s="70">
+        <v>2.9895833333333333E-2</v>
+      </c>
+      <c r="DB8" s="33">
+        <f t="shared" si="22"/>
+        <v>2.1909722222222223E-2</v>
+      </c>
+      <c r="DC8" s="31">
+        <v>2</v>
+      </c>
+      <c r="DD8" s="70">
+        <v>3.2824074074074075E-2</v>
+      </c>
+      <c r="DE8" s="33">
+        <f t="shared" si="23"/>
+        <v>2.4837962962962964E-2</v>
+      </c>
+      <c r="DF8" s="31"/>
+      <c r="DG8" s="70"/>
+      <c r="DH8" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI8" s="31">
+        <v>3</v>
+      </c>
+      <c r="DJ8" s="70">
+        <v>8.5300925925925926E-3</v>
+      </c>
+      <c r="DK8" s="33">
+        <f t="shared" si="25"/>
+        <v>5.4398148148148209E-4</v>
+      </c>
+      <c r="DL8" s="31">
+        <v>3</v>
+      </c>
+      <c r="DM8" s="70">
+        <v>9.6874999999999999E-3</v>
+      </c>
+      <c r="DN8" s="33">
+        <f t="shared" si="26"/>
+        <v>1.7013888888888894E-3</v>
+      </c>
+      <c r="DO8" s="31"/>
+      <c r="DP8" s="70"/>
+      <c r="DQ8" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR8" s="35"/>
     </row>
-    <row r="9" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>149</v>
       </c>
@@ -3109,7 +3798,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L5</v>
       </c>
       <c r="G9" s="5">
@@ -3145,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="Q9" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.2777777777777812E-2</v>
       </c>
       <c r="R9" s="6" t="s">
@@ -3161,38 +3850,58 @@
         <v>156</v>
       </c>
       <c r="V9" s="8"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="20"/>
+      <c r="W9" s="19">
+        <v>2.9282407407407406E-2</v>
+      </c>
+      <c r="X9" s="20">
+        <v>2.4074074074074074E-2</v>
+      </c>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
       <c r="AA9" s="20"/>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD9" s="20"/>
-      <c r="AE9" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.3356481481481477E-2</v>
+      </c>
+      <c r="AD9" s="20">
+        <v>5.2662037037037035E-3</v>
+      </c>
+      <c r="AE9" s="20">
+        <v>3.8888888888888888E-3</v>
+      </c>
       <c r="AF9" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG9" s="21"/>
-      <c r="AH9" s="21"/>
+        <v>4.4201388888888887E-2</v>
+      </c>
+      <c r="AG9" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH9" s="21">
+        <v>25</v>
+      </c>
       <c r="AI9" s="22"/>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="30"/>
+      <c r="AJ9" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="30">
+        <v>4</v>
+      </c>
       <c r="AL9" s="31"/>
       <c r="AM9" s="34"/>
       <c r="AN9" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="32"/>
-      <c r="AQ9" s="33" t="str">
+      <c r="AO9" s="31">
+        <v>7</v>
+      </c>
+      <c r="AP9" s="34">
+        <v>5.6365740740740742E-3</v>
+      </c>
+      <c r="AQ9" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>3.7037037037037073E-4</v>
       </c>
       <c r="AR9" s="31"/>
       <c r="AS9" s="32"/>
@@ -3212,11 +3921,15 @@
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA9" s="31"/>
-      <c r="BB9" s="32"/>
-      <c r="BC9" s="33" t="str">
+      <c r="BA9" s="31">
+        <v>1</v>
+      </c>
+      <c r="BB9" s="34">
+        <v>1.1458333333333333E-2</v>
+      </c>
+      <c r="BC9" s="33">
         <f t="shared" si="6"/>
-        <v>NA</v>
+        <v>6.192129629629629E-3</v>
       </c>
       <c r="BD9" s="31"/>
       <c r="BE9" s="32"/>
@@ -3231,16 +3944,20 @@
         <v>NA</v>
       </c>
       <c r="BJ9" s="31"/>
-      <c r="BK9" s="34"/>
+      <c r="BK9" s="32"/>
       <c r="BL9" s="33" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM9" s="31"/>
-      <c r="BN9" s="32"/>
-      <c r="BO9" s="33" t="str">
+      <c r="BM9" s="31">
+        <v>1</v>
+      </c>
+      <c r="BN9" s="34">
+        <v>2.6817129629629628E-2</v>
+      </c>
+      <c r="BO9" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>2.1550925925925925E-2</v>
       </c>
       <c r="BP9" s="31"/>
       <c r="BQ9" s="32"/>
@@ -3257,60 +3974,110 @@
       <c r="BV9" s="31"/>
       <c r="BW9" s="32"/>
       <c r="BX9" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY9" s="31"/>
+      <c r="BZ9" s="32"/>
+      <c r="CA9" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY9" s="31"/>
-      <c r="BZ9" s="56"/>
-      <c r="CA9" s="33" t="str">
+      <c r="CB9" s="31"/>
+      <c r="CC9" s="56"/>
+      <c r="CD9" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB9" s="31"/>
-      <c r="CC9" s="32"/>
-      <c r="CD9" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE9" s="31"/>
       <c r="CF9" s="32"/>
       <c r="CG9" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH9" s="31"/>
       <c r="CI9" s="32"/>
       <c r="CJ9" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK9" s="31"/>
       <c r="CL9" s="32"/>
       <c r="CM9" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN9" s="31"/>
       <c r="CO9" s="32"/>
       <c r="CP9" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ9" s="31"/>
+      <c r="CR9" s="32"/>
+      <c r="CS9" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="CQ9" s="31"/>
-      <c r="CR9" s="56"/>
-      <c r="CS9" s="33" t="str">
-        <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT9" s="31"/>
       <c r="CU9" s="56"/>
       <c r="CV9" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW9" s="31"/>
+      <c r="CX9" s="56"/>
+      <c r="CY9" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW9" s="35"/>
+      <c r="CZ9" s="31"/>
+      <c r="DA9" s="56"/>
+      <c r="DB9" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC9" s="31">
+        <v>4</v>
+      </c>
+      <c r="DD9" s="56">
+        <v>1.2442129629629629E-2</v>
+      </c>
+      <c r="DE9" s="33">
+        <f t="shared" si="23"/>
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="DF9" s="31"/>
+      <c r="DG9" s="56"/>
+      <c r="DH9" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI9" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ9" s="56">
+        <v>1.9756944444444445E-2</v>
+      </c>
+      <c r="DK9" s="33">
+        <f t="shared" si="25"/>
+        <v>1.4490740740740742E-2</v>
+      </c>
+      <c r="DL9" s="31"/>
+      <c r="DM9" s="56"/>
+      <c r="DN9" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO9" s="31"/>
+      <c r="DP9" s="56"/>
+      <c r="DQ9" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR9" s="35"/>
     </row>
-    <row r="10" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>149</v>
       </c>
@@ -3327,7 +4094,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L6</v>
       </c>
       <c r="G10" s="5">
@@ -3363,7 +4130,7 @@
         <v>3</v>
       </c>
       <c r="Q10" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>7.0833333333333359E-2</v>
       </c>
       <c r="R10" s="6" t="s">
@@ -3379,32 +4146,54 @@
         <v>165</v>
       </c>
       <c r="V10" s="8"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
+      <c r="W10" s="19">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="X10" s="20">
+        <v>2.2881944444444444E-2</v>
+      </c>
+      <c r="Y10" s="20">
+        <v>1.3935185185185186E-2</v>
+      </c>
       <c r="Z10" s="20"/>
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
       <c r="AC10" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="20"/>
-      <c r="AE10" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.9317129629629636E-2</v>
+      </c>
+      <c r="AD10" s="20">
+        <v>4.2708333333333331E-3</v>
+      </c>
+      <c r="AE10" s="20">
+        <v>1.0416666666666666E-2</v>
+      </c>
       <c r="AF10" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="21"/>
-      <c r="AH10" s="21"/>
+        <v>4.4629629629629637E-2</v>
+      </c>
+      <c r="AG10" s="21">
+        <v>60</v>
+      </c>
+      <c r="AH10" s="21">
+        <v>95</v>
+      </c>
       <c r="AI10" s="22"/>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="30"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="34"/>
-      <c r="AN10" s="33" t="str">
+      <c r="AJ10" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="30">
+        <v>3</v>
+      </c>
+      <c r="AL10" s="31">
+        <v>1</v>
+      </c>
+      <c r="AM10" s="34">
+        <v>1.3229166666666667E-2</v>
+      </c>
+      <c r="AN10" s="33">
         <f t="shared" si="1"/>
-        <v>NA</v>
+        <v>8.9583333333333338E-3</v>
       </c>
       <c r="AO10" s="31"/>
       <c r="AP10" s="34"/>
@@ -3454,11 +4243,15 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM10" s="31"/>
-      <c r="BN10" s="32"/>
-      <c r="BO10" s="33" t="str">
+      <c r="BM10" s="31">
+        <v>1</v>
+      </c>
+      <c r="BN10" s="34">
+        <v>1.5925925925925927E-2</v>
+      </c>
+      <c r="BO10" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>1.1655092592592594E-2</v>
       </c>
       <c r="BP10" s="31"/>
       <c r="BQ10" s="32"/>
@@ -3475,60 +4268,118 @@
       <c r="BV10" s="31"/>
       <c r="BW10" s="32"/>
       <c r="BX10" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY10" s="31"/>
+      <c r="BZ10" s="32"/>
+      <c r="CA10" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY10" s="31"/>
-      <c r="BZ10" s="56"/>
-      <c r="CA10" s="33" t="str">
+      <c r="CB10" s="31"/>
+      <c r="CC10" s="56"/>
+      <c r="CD10" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB10" s="31"/>
-      <c r="CC10" s="34"/>
-      <c r="CD10" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE10" s="31"/>
       <c r="CF10" s="34"/>
       <c r="CG10" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH10" s="31"/>
       <c r="CI10" s="34"/>
       <c r="CJ10" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK10" s="31"/>
       <c r="CL10" s="34"/>
       <c r="CM10" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN10" s="31"/>
       <c r="CO10" s="34"/>
       <c r="CP10" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ10" s="31"/>
       <c r="CR10" s="34"/>
       <c r="CS10" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT10" s="31"/>
       <c r="CU10" s="34"/>
       <c r="CV10" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW10" s="31"/>
+      <c r="CX10" s="34"/>
+      <c r="CY10" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW10" s="35"/>
+      <c r="CZ10" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA10" s="34">
+        <v>1.2025462962962963E-2</v>
+      </c>
+      <c r="DB10" s="33">
+        <f t="shared" si="22"/>
+        <v>7.7546296296296304E-3</v>
+      </c>
+      <c r="DC10" s="31">
+        <v>5</v>
+      </c>
+      <c r="DD10" s="34">
+        <v>1.0254629629629629E-2</v>
+      </c>
+      <c r="DE10" s="33">
+        <f t="shared" si="23"/>
+        <v>5.9837962962962961E-3</v>
+      </c>
+      <c r="DF10" s="31">
+        <v>2</v>
+      </c>
+      <c r="DG10" s="34">
+        <v>2.3252314814814816E-2</v>
+      </c>
+      <c r="DH10" s="33">
+        <f t="shared" si="24"/>
+        <v>1.8981481481481481E-2</v>
+      </c>
+      <c r="DI10" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ10" s="34">
+        <v>1.3819444444444445E-2</v>
+      </c>
+      <c r="DK10" s="33">
+        <f t="shared" si="25"/>
+        <v>9.5486111111111119E-3</v>
+      </c>
+      <c r="DL10" s="31"/>
+      <c r="DM10" s="34"/>
+      <c r="DN10" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO10" s="31"/>
+      <c r="DP10" s="34"/>
+      <c r="DQ10" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR10" s="35"/>
     </row>
-    <row r="11" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>149</v>
       </c>
@@ -3545,7 +4396,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L3</v>
       </c>
       <c r="G11" s="5">
@@ -3581,7 +4432,7 @@
         <v>3</v>
       </c>
       <c r="Q11" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>9.7916666666666652E-2</v>
       </c>
       <c r="R11" s="6" t="s">
@@ -3597,38 +4448,58 @@
         <v>156</v>
       </c>
       <c r="V11" s="8"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="20"/>
-      <c r="Y11" s="20"/>
+      <c r="W11" s="19">
+        <v>2.7708333333333335E-2</v>
+      </c>
+      <c r="X11" s="20">
+        <v>2.0474537037037038E-2</v>
+      </c>
+      <c r="Y11" s="20">
+        <v>8.1481481481481474E-3</v>
+      </c>
       <c r="Z11" s="20"/>
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.6331018518518523E-2</v>
+      </c>
+      <c r="AD11" s="20">
+        <v>1.0416666666666666E-2</v>
+      </c>
       <c r="AE11" s="20"/>
       <c r="AF11" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="21"/>
-      <c r="AH11" s="21"/>
+        <v>4.5914351851851859E-2</v>
+      </c>
+      <c r="AG11" s="21">
+        <v>80</v>
+      </c>
+      <c r="AH11" s="21">
+        <v>95</v>
+      </c>
       <c r="AI11" s="22"/>
-      <c r="AJ11" s="29"/>
-      <c r="AK11" s="30"/>
+      <c r="AJ11" s="29">
+        <v>3</v>
+      </c>
+      <c r="AK11" s="30">
+        <v>3</v>
+      </c>
       <c r="AL11" s="31"/>
       <c r="AM11" s="34"/>
       <c r="AN11" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO11" s="31"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="33" t="str">
+      <c r="AO11" s="31">
+        <v>6</v>
+      </c>
+      <c r="AP11" s="34">
+        <v>2.0173611111111111E-2</v>
+      </c>
+      <c r="AQ11" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>9.7569444444444448E-3</v>
       </c>
       <c r="AR11" s="31"/>
       <c r="AS11" s="32"/>
@@ -3661,25 +4532,29 @@
         <v>NA</v>
       </c>
       <c r="BG11" s="31"/>
-      <c r="BH11" s="34"/>
+      <c r="BH11" s="32"/>
       <c r="BI11" s="33" t="str">
         <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="BJ11" s="31"/>
-      <c r="BK11" s="32"/>
+      <c r="BK11" s="34"/>
       <c r="BL11" s="33" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM11" s="31"/>
-      <c r="BN11" s="34"/>
-      <c r="BO11" s="33" t="str">
+      <c r="BM11" s="31">
+        <v>1</v>
+      </c>
+      <c r="BN11" s="34">
+        <v>2.1747685185185186E-2</v>
+      </c>
+      <c r="BO11" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>1.133101851851852E-2</v>
       </c>
       <c r="BP11" s="31"/>
-      <c r="BQ11" s="32"/>
+      <c r="BQ11" s="34"/>
       <c r="BR11" s="33" t="str">
         <f t="shared" si="11"/>
         <v>NA</v>
@@ -3693,60 +4568,106 @@
       <c r="BV11" s="31"/>
       <c r="BW11" s="32"/>
       <c r="BX11" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY11" s="31"/>
+      <c r="BZ11" s="32"/>
+      <c r="CA11" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY11" s="31"/>
-      <c r="BZ11" s="56"/>
-      <c r="CA11" s="33" t="str">
+      <c r="CB11" s="31"/>
+      <c r="CC11" s="56"/>
+      <c r="CD11" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB11" s="31"/>
-      <c r="CC11" s="34"/>
-      <c r="CD11" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE11" s="31"/>
       <c r="CF11" s="34"/>
       <c r="CG11" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH11" s="31"/>
       <c r="CI11" s="34"/>
       <c r="CJ11" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK11" s="31"/>
       <c r="CL11" s="34"/>
       <c r="CM11" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN11" s="31"/>
       <c r="CO11" s="34"/>
       <c r="CP11" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ11" s="31"/>
       <c r="CR11" s="34"/>
       <c r="CS11" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT11" s="31"/>
       <c r="CU11" s="34"/>
       <c r="CV11" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW11" s="31"/>
+      <c r="CX11" s="34"/>
+      <c r="CY11" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW11" s="35"/>
+      <c r="CZ11" s="31"/>
+      <c r="DA11" s="34"/>
+      <c r="DB11" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC11" s="31">
+        <v>2</v>
+      </c>
+      <c r="DD11" s="34">
+        <v>2.1666666666666667E-2</v>
+      </c>
+      <c r="DE11" s="33">
+        <f t="shared" si="23"/>
+        <v>1.1250000000000001E-2</v>
+      </c>
+      <c r="DF11" s="31"/>
+      <c r="DG11" s="34"/>
+      <c r="DH11" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI11" s="31"/>
+      <c r="DJ11" s="34"/>
+      <c r="DK11" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL11" s="31"/>
+      <c r="DM11" s="34"/>
+      <c r="DN11" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO11" s="31"/>
+      <c r="DP11" s="34"/>
+      <c r="DQ11" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR11" s="35"/>
     </row>
-    <row r="12" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>149</v>
       </c>
@@ -3763,7 +4684,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D1</v>
       </c>
       <c r="G12" s="5">
@@ -3799,7 +4720,7 @@
         <v>3</v>
       </c>
       <c r="Q12" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>9.7222222222222265E-2</v>
       </c>
       <c r="R12" s="6" t="s">
@@ -3815,38 +4736,58 @@
         <v>156</v>
       </c>
       <c r="V12" s="8"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="20"/>
+      <c r="W12" s="19">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="X12" s="20">
+        <v>1.7847222222222223E-2</v>
+      </c>
+      <c r="Y12" s="20">
+        <v>1.0937499999999999E-2</v>
+      </c>
       <c r="Z12" s="20"/>
       <c r="AA12" s="20"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.6643518518518515E-2</v>
+      </c>
+      <c r="AD12" s="20">
+        <v>3.6458333333333334E-3</v>
+      </c>
       <c r="AE12" s="20"/>
       <c r="AF12" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG12" s="21"/>
-      <c r="AH12" s="21"/>
+        <v>4.299768518518518E-2</v>
+      </c>
+      <c r="AG12" s="21">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="21">
+        <v>100</v>
+      </c>
       <c r="AI12" s="22"/>
-      <c r="AJ12" s="29"/>
-      <c r="AK12" s="30"/>
+      <c r="AJ12" s="29">
+        <v>4</v>
+      </c>
+      <c r="AK12" s="30">
+        <v>3</v>
+      </c>
       <c r="AL12" s="31"/>
       <c r="AM12" s="34"/>
       <c r="AN12" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="32"/>
-      <c r="AQ12" s="33" t="str">
+      <c r="AO12" s="31">
+        <v>3</v>
+      </c>
+      <c r="AP12" s="34">
+        <v>6.5972222222222222E-3</v>
+      </c>
+      <c r="AQ12" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>2.9513888888888888E-3</v>
       </c>
       <c r="AR12" s="31"/>
       <c r="AS12" s="32"/>
@@ -3890,17 +4831,25 @@
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM12" s="31"/>
-      <c r="BN12" s="32"/>
-      <c r="BO12" s="33" t="str">
+      <c r="BM12" s="31">
+        <v>6</v>
+      </c>
+      <c r="BN12" s="34">
+        <v>3.6458333333333334E-3</v>
+      </c>
+      <c r="BO12" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
-      </c>
-      <c r="BP12" s="31"/>
-      <c r="BQ12" s="32"/>
-      <c r="BR12" s="33" t="str">
+        <v>0</v>
+      </c>
+      <c r="BP12" s="31">
+        <v>1</v>
+      </c>
+      <c r="BQ12" s="34">
+        <v>2.7442129629629629E-2</v>
+      </c>
+      <c r="BR12" s="33">
         <f t="shared" si="11"/>
-        <v>NA</v>
+        <v>2.3796296296296295E-2</v>
       </c>
       <c r="BS12" s="31"/>
       <c r="BT12" s="32"/>
@@ -3911,60 +4860,106 @@
       <c r="BV12" s="31"/>
       <c r="BW12" s="32"/>
       <c r="BX12" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY12" s="31"/>
+      <c r="BZ12" s="32"/>
+      <c r="CA12" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY12" s="31"/>
-      <c r="BZ12" s="56"/>
-      <c r="CA12" s="33" t="str">
+      <c r="CB12" s="31"/>
+      <c r="CC12" s="56"/>
+      <c r="CD12" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB12" s="31"/>
-      <c r="CC12" s="70"/>
-      <c r="CD12" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE12" s="31"/>
       <c r="CF12" s="70"/>
       <c r="CG12" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH12" s="31"/>
       <c r="CI12" s="70"/>
       <c r="CJ12" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK12" s="31"/>
       <c r="CL12" s="70"/>
       <c r="CM12" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN12" s="31"/>
       <c r="CO12" s="70"/>
       <c r="CP12" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ12" s="31"/>
       <c r="CR12" s="70"/>
       <c r="CS12" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT12" s="31"/>
       <c r="CU12" s="70"/>
       <c r="CV12" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW12" s="31"/>
+      <c r="CX12" s="70"/>
+      <c r="CY12" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW12" s="35"/>
+      <c r="CZ12" s="31"/>
+      <c r="DA12" s="70"/>
+      <c r="DB12" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC12" s="31"/>
+      <c r="DD12" s="70"/>
+      <c r="DE12" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>NA</v>
+      </c>
+      <c r="DF12" s="31">
+        <v>3</v>
+      </c>
+      <c r="DG12" s="70">
+        <v>3.6458333333333334E-3</v>
+      </c>
+      <c r="DH12" s="33">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="DI12" s="31"/>
+      <c r="DJ12" s="70"/>
+      <c r="DK12" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL12" s="31"/>
+      <c r="DM12" s="70"/>
+      <c r="DN12" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO12" s="31"/>
+      <c r="DP12" s="70"/>
+      <c r="DQ12" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR12" s="35"/>
     </row>
-    <row r="13" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>149</v>
       </c>
@@ -3981,7 +4976,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L2</v>
       </c>
       <c r="G13" s="5">
@@ -4017,7 +5012,7 @@
         <v>3</v>
       </c>
       <c r="Q13" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>8.7500000000000022E-2</v>
       </c>
       <c r="R13" s="6" t="s">
@@ -4033,38 +5028,58 @@
         <v>156</v>
       </c>
       <c r="V13" s="8"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="20"/>
-      <c r="Y13" s="20"/>
+      <c r="W13" s="19">
+        <v>2.2187499999999999E-2</v>
+      </c>
+      <c r="X13" s="20">
+        <v>1.9004629629629628E-2</v>
+      </c>
+      <c r="Y13" s="20">
+        <v>1.0069444444444445E-2</v>
+      </c>
       <c r="Z13" s="20"/>
       <c r="AA13" s="20"/>
       <c r="AB13" s="20"/>
       <c r="AC13" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD13" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.1261574074074071E-2</v>
+      </c>
+      <c r="AD13" s="20">
+        <v>7.2337962962962963E-3</v>
+      </c>
       <c r="AE13" s="20"/>
       <c r="AF13" s="20">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
+        <v>4.4027777777777777E-2</v>
+      </c>
+      <c r="AG13" s="21">
+        <v>80</v>
+      </c>
+      <c r="AH13" s="21">
+        <v>85</v>
+      </c>
       <c r="AI13" s="22"/>
-      <c r="AJ13" s="29"/>
-      <c r="AK13" s="30"/>
+      <c r="AJ13" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK13" s="30">
+        <v>4</v>
+      </c>
       <c r="AL13" s="31"/>
       <c r="AM13" s="34"/>
       <c r="AN13" s="33" t="str">
         <f t="shared" si="1"/>
         <v>NA</v>
       </c>
-      <c r="AO13" s="31"/>
-      <c r="AP13" s="32"/>
-      <c r="AQ13" s="33" t="str">
+      <c r="AO13" s="31">
+        <v>9</v>
+      </c>
+      <c r="AP13" s="34">
+        <v>7.2453703703703708E-3</v>
+      </c>
+      <c r="AQ13" s="33">
         <f t="shared" si="2"/>
-        <v>NA</v>
+        <v>1.1574074074074438E-5</v>
       </c>
       <c r="AR13" s="31"/>
       <c r="AS13" s="32"/>
@@ -4090,29 +5105,37 @@
         <f t="shared" si="6"/>
         <v>NA</v>
       </c>
-      <c r="BD13" s="31"/>
-      <c r="BE13" s="32"/>
-      <c r="BF13" s="33" t="str">
+      <c r="BD13" s="31">
+        <v>1</v>
+      </c>
+      <c r="BE13" s="34">
+        <v>2.4710648148148148E-2</v>
+      </c>
+      <c r="BF13" s="33">
         <f t="shared" si="7"/>
-        <v>NA</v>
+        <v>1.7476851851851851E-2</v>
       </c>
       <c r="BG13" s="31"/>
-      <c r="BH13" s="34"/>
+      <c r="BH13" s="32"/>
       <c r="BI13" s="33" t="str">
         <f t="shared" si="8"/>
         <v>NA</v>
       </c>
       <c r="BJ13" s="31"/>
-      <c r="BK13" s="32"/>
+      <c r="BK13" s="34"/>
       <c r="BL13" s="33" t="str">
         <f t="shared" si="9"/>
         <v>NA</v>
       </c>
-      <c r="BM13" s="31"/>
-      <c r="BN13" s="32"/>
-      <c r="BO13" s="33" t="str">
+      <c r="BM13" s="31">
+        <v>4</v>
+      </c>
+      <c r="BN13" s="34">
+        <v>7.3379629629629628E-3</v>
+      </c>
+      <c r="BO13" s="33">
         <f t="shared" si="10"/>
-        <v>NA</v>
+        <v>1.0416666666666647E-4</v>
       </c>
       <c r="BP13" s="31"/>
       <c r="BQ13" s="32"/>
@@ -4121,68 +5144,118 @@
         <v>NA</v>
       </c>
       <c r="BS13" s="31"/>
-      <c r="BT13" s="34"/>
+      <c r="BT13" s="32"/>
       <c r="BU13" s="33" t="str">
         <f t="shared" si="12"/>
         <v>NA</v>
       </c>
       <c r="BV13" s="31"/>
-      <c r="BW13" s="32"/>
+      <c r="BW13" s="34"/>
       <c r="BX13" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v>NA</v>
+      </c>
+      <c r="BY13" s="31"/>
+      <c r="BZ13" s="32"/>
+      <c r="CA13" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY13" s="31"/>
-      <c r="BZ13" s="56"/>
-      <c r="CA13" s="33" t="str">
+      <c r="CB13" s="31"/>
+      <c r="CC13" s="56"/>
+      <c r="CD13" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB13" s="31"/>
-      <c r="CC13" s="32"/>
-      <c r="CD13" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE13" s="31"/>
       <c r="CF13" s="32"/>
       <c r="CG13" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH13" s="31"/>
       <c r="CI13" s="32"/>
       <c r="CJ13" s="33" t="str">
+        <f t="shared" si="16"/>
+        <v>NA</v>
+      </c>
+      <c r="CK13" s="31"/>
+      <c r="CL13" s="32"/>
+      <c r="CM13" s="33" t="str">
         <f t="shared" si="17"/>
-        <v>NA</v>
-      </c>
-      <c r="CK13" s="31"/>
-      <c r="CL13" s="34"/>
-      <c r="CM13" s="33" t="str">
-        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CN13" s="31"/>
       <c r="CO13" s="34"/>
       <c r="CP13" s="33" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ13" s="31"/>
+      <c r="CR13" s="34"/>
+      <c r="CS13" s="33" t="str">
         <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="CQ13" s="31"/>
-      <c r="CR13" s="32"/>
-      <c r="CS13" s="33" t="str">
-        <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT13" s="31"/>
       <c r="CU13" s="32"/>
       <c r="CV13" s="33" t="str">
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW13" s="31"/>
+      <c r="CX13" s="32"/>
+      <c r="CY13" s="33" t="str">
         <f t="shared" si="21"/>
         <v>NA</v>
       </c>
-      <c r="CW13" s="35"/>
+      <c r="CZ13" s="31"/>
+      <c r="DA13" s="32"/>
+      <c r="DB13" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC13" s="31">
+        <v>2</v>
+      </c>
+      <c r="DD13" s="34">
+        <v>8.5532407407407415E-3</v>
+      </c>
+      <c r="DE13" s="33">
+        <f t="shared" si="23"/>
+        <v>1.3194444444444451E-3</v>
+      </c>
+      <c r="DF13" s="31"/>
+      <c r="DG13" s="32"/>
+      <c r="DH13" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI13" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ13" s="34">
+        <v>2.8472222222222222E-2</v>
+      </c>
+      <c r="DK13" s="33">
+        <f t="shared" si="25"/>
+        <v>2.1238425925925924E-2</v>
+      </c>
+      <c r="DL13" s="31"/>
+      <c r="DM13" s="32"/>
+      <c r="DN13" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO13" s="31"/>
+      <c r="DP13" s="32"/>
+      <c r="DQ13" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR13" s="35"/>
     </row>
-    <row r="14" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>149</v>
       </c>
@@ -4199,7 +5272,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>L1</v>
       </c>
       <c r="G14" s="5">
@@ -4235,7 +5308,7 @@
         <v>5</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>7.1527777777777801E-2</v>
       </c>
       <c r="R14" s="6" t="s">
@@ -4251,49 +5324,71 @@
         <v>156</v>
       </c>
       <c r="V14" s="8"/>
-      <c r="W14" s="19"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
+      <c r="W14" s="19">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="X14" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="Y14" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="Z14" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="AA14" s="20">
+        <v>9.9421296296296289E-3</v>
+      </c>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="20"/>
+        <f t="shared" si="30"/>
+        <v>6.9386574074074073E-2</v>
+      </c>
+      <c r="AD14" s="20">
+        <v>3.9930555555555552E-3</v>
+      </c>
+      <c r="AE14" s="20">
+        <v>2.0358796296296295E-2</v>
+      </c>
       <c r="AF14" s="20">
-        <f t="shared" ref="AF14:AF22" si="25">AC14-AD14-AE14</f>
-        <v>0</v>
-      </c>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
+        <f t="shared" ref="AF14:AF22" si="32">AC14-AD14-AE14</f>
+        <v>4.5034722222222226E-2</v>
+      </c>
+      <c r="AG14" s="21">
+        <v>60</v>
+      </c>
+      <c r="AH14" s="21">
+        <v>100</v>
+      </c>
       <c r="AI14" s="22"/>
-      <c r="AJ14" s="29"/>
-      <c r="AK14" s="30"/>
+      <c r="AJ14" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="30">
+        <v>3</v>
+      </c>
       <c r="AL14" s="31"/>
       <c r="AM14" s="32"/>
       <c r="AN14" s="33" t="str">
-        <f t="shared" ref="AN14:AN22" si="26">IF(AL14=0,"NA",AM14-$AD14)</f>
+        <f t="shared" ref="AN14:AN22" si="33">IF(AL14=0,"NA",AM14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AO14" s="31"/>
       <c r="AP14" s="32"/>
       <c r="AQ14" s="33" t="str">
-        <f t="shared" ref="AQ14:AQ22" si="27">IF(AO14=0,"NA",AP14-$AD14)</f>
+        <f t="shared" ref="AQ14:AQ22" si="34">IF(AO14=0,"NA",AP14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AR14" s="31"/>
       <c r="AS14" s="32"/>
       <c r="AT14" s="33" t="str">
-        <f t="shared" ref="AT14:AT22" si="28">IF(AR14=0,"NA",AS14-$AD14)</f>
+        <f t="shared" ref="AT14:AT22" si="35">IF(AR14=0,"NA",AS14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AU14" s="31"/>
       <c r="AV14" s="32"/>
       <c r="AW14" s="33" t="str">
-        <f t="shared" ref="AW14:AW22" si="29">IF(AU14=0,"NA",AV14-$AD14)</f>
+        <f t="shared" ref="AW14:AW22" si="36">IF(AU14=0,"NA",AV14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="AX14" s="31"/>
@@ -4305,102 +5400,164 @@
       <c r="BA14" s="31"/>
       <c r="BB14" s="34"/>
       <c r="BC14" s="33" t="str">
-        <f t="shared" ref="BC14:BC22" si="30">IF(BA14=0,"NA",BB14-$AD14)</f>
+        <f t="shared" ref="BC14:BC22" si="37">IF(BA14=0,"NA",BB14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BD14" s="31"/>
       <c r="BE14" s="32"/>
       <c r="BF14" s="33" t="str">
-        <f t="shared" ref="BF14:BF22" si="31">IF(BD14=0,"NA",BE14-$AD14)</f>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG14" s="31"/>
-      <c r="BH14" s="34"/>
+      <c r="BH14" s="32"/>
       <c r="BI14" s="33" t="str">
-        <f t="shared" ref="BI14:BI22" si="32">IF(BG14=0,"NA",BH14-$AD14)</f>
+        <f t="shared" ref="BI14:BI22" si="38">IF(BG14=0,"NA",BH14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BJ14" s="31"/>
       <c r="BK14" s="34"/>
       <c r="BL14" s="33" t="str">
-        <f t="shared" ref="BL14:BL22" si="33">IF(BJ14=0,"NA",BK14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="BM14" s="31"/>
-      <c r="BN14" s="32"/>
-      <c r="BO14" s="33" t="str">
-        <f t="shared" ref="BO14:BO22" si="34">IF(BM14=0,"NA",BN14-$AD14)</f>
-        <v>NA</v>
+        <f t="shared" ref="BL14:BL22" si="39">IF(BJ14=0,"NA",BK14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="BM14" s="31">
+        <v>16</v>
+      </c>
+      <c r="BN14" s="34">
+        <v>3.9930555555555552E-3</v>
+      </c>
+      <c r="BO14" s="33">
+        <f t="shared" ref="BO14:BO22" si="40">IF(BM14=0,"NA",BN14-$AD14)</f>
+        <v>0</v>
       </c>
       <c r="BP14" s="31"/>
       <c r="BQ14" s="32"/>
       <c r="BR14" s="33" t="str">
-        <f t="shared" ref="BR14:BR22" si="35">IF(BP14=0,"NA",BQ14-$AD14)</f>
+        <f t="shared" ref="BR14:BR22" si="41">IF(BP14=0,"NA",BQ14-$AD14)</f>
         <v>NA</v>
       </c>
       <c r="BS14" s="31"/>
-      <c r="BT14" s="34"/>
+      <c r="BT14" s="32"/>
       <c r="BU14" s="33" t="str">
-        <f t="shared" ref="BU14:BU22" si="36">IF(BS14=0,"NA",BT14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="BV14" s="31"/>
-      <c r="BW14" s="34"/>
-      <c r="BX14" s="33" t="str">
+        <f t="shared" ref="BU14:BU22" si="42">IF(BS14=0,"NA",BT14-$AD14)</f>
+        <v>NA</v>
+      </c>
+      <c r="BV14" s="31">
+        <v>1</v>
+      </c>
+      <c r="BW14" s="34">
+        <v>8.0439814814814818E-3</v>
+      </c>
+      <c r="BX14" s="33">
+        <f t="shared" ref="BX14:BX22" si="43">IF(BV14=0,"NA",BW14-$AD14)</f>
+        <v>4.0509259259259266E-3</v>
+      </c>
+      <c r="BY14" s="31"/>
+      <c r="BZ14" s="34"/>
+      <c r="CA14" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY14" s="31"/>
-      <c r="BZ14" s="56"/>
-      <c r="CA14" s="33" t="str">
+      <c r="CB14" s="31"/>
+      <c r="CC14" s="56"/>
+      <c r="CD14" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB14" s="31"/>
-      <c r="CC14" s="32"/>
-      <c r="CD14" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE14" s="31"/>
       <c r="CF14" s="32"/>
       <c r="CG14" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH14" s="31"/>
       <c r="CI14" s="32"/>
       <c r="CJ14" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK14" s="31"/>
       <c r="CL14" s="32"/>
       <c r="CM14" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN14" s="31"/>
       <c r="CO14" s="32"/>
       <c r="CP14" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ14" s="31"/>
       <c r="CR14" s="32"/>
       <c r="CS14" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT14" s="31"/>
       <c r="CU14" s="32"/>
       <c r="CV14" s="33" t="str">
-        <f t="shared" ref="CV14:CV22" si="37">IF(CT14=0,"NA",CU14-$AD14)</f>
-        <v>NA</v>
-      </c>
-      <c r="CW14" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW14" s="31"/>
+      <c r="CX14" s="32"/>
+      <c r="CY14" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ14" s="31"/>
+      <c r="DA14" s="32"/>
+      <c r="DB14" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DD14" s="34">
+        <v>5.3935185185185188E-3</v>
+      </c>
+      <c r="DE14" s="33">
+        <f t="shared" ref="DE14:DE22" si="44">IF(DC14=0,"NA",DD14-$AD14)</f>
+        <v>1.4004629629629636E-3</v>
+      </c>
+      <c r="DF14" s="31"/>
+      <c r="DG14" s="32"/>
+      <c r="DH14" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ14" s="34">
+        <v>9.1087962962962971E-3</v>
+      </c>
+      <c r="DK14" s="33">
+        <f t="shared" si="25"/>
+        <v>5.1157407407407419E-3</v>
+      </c>
+      <c r="DL14" s="31"/>
+      <c r="DM14" s="32"/>
+      <c r="DN14" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO14" s="31">
+        <v>1</v>
+      </c>
+      <c r="DP14" s="34">
+        <v>1.3495370370370371E-2</v>
+      </c>
+      <c r="DQ14" s="33">
+        <f t="shared" si="27"/>
+        <v>9.5023148148148159E-3</v>
+      </c>
+      <c r="DR14" s="35"/>
     </row>
-    <row r="15" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>149</v>
       </c>
@@ -4417,7 +5574,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D2</v>
       </c>
       <c r="G15" s="5">
@@ -4453,7 +5610,7 @@
         <v>4</v>
       </c>
       <c r="Q15" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>6.0416666666666619E-2</v>
       </c>
       <c r="R15" s="6" t="s">
@@ -4469,49 +5626,69 @@
         <v>156</v>
       </c>
       <c r="V15" s="8"/>
-      <c r="W15" s="19"/>
-      <c r="X15" s="20"/>
-      <c r="Y15" s="20"/>
-      <c r="Z15" s="20"/>
+      <c r="W15" s="19">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="X15" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y15" s="20">
+        <v>1.7847222222222223E-2</v>
+      </c>
+      <c r="Z15" s="20">
+        <v>9.6064814814814819E-4</v>
+      </c>
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
+        <f t="shared" si="30"/>
+        <v>5.4525462962962963E-2</v>
+      </c>
+      <c r="AD15" s="20">
+        <v>3.9930555555555552E-3</v>
+      </c>
+      <c r="AE15" s="20">
+        <v>6.9444444444444441E-3</v>
+      </c>
       <c r="AF15" s="20">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
+        <f t="shared" si="32"/>
+        <v>4.3587962962962967E-2</v>
+      </c>
+      <c r="AG15" s="21">
+        <v>90</v>
+      </c>
+      <c r="AH15" s="21">
+        <v>90</v>
+      </c>
       <c r="AI15" s="22"/>
-      <c r="AJ15" s="29"/>
-      <c r="AK15" s="30"/>
+      <c r="AJ15" s="29">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="30">
+        <v>5</v>
+      </c>
       <c r="AL15" s="31"/>
       <c r="AM15" s="34"/>
       <c r="AN15" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO15" s="31"/>
       <c r="AP15" s="32"/>
       <c r="AQ15" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR15" s="31"/>
       <c r="AS15" s="32"/>
       <c r="AT15" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU15" s="31"/>
       <c r="AV15" s="32"/>
       <c r="AW15" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX15" s="31"/>
@@ -4523,102 +5700,164 @@
       <c r="BA15" s="31"/>
       <c r="BB15" s="32"/>
       <c r="BC15" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD15" s="31"/>
       <c r="BE15" s="32"/>
       <c r="BF15" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG15" s="31"/>
-      <c r="BH15" s="34"/>
+      <c r="BH15" s="32"/>
       <c r="BI15" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ15" s="31"/>
-      <c r="BK15" s="32"/>
+      <c r="BK15" s="34"/>
       <c r="BL15" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BM15" s="31"/>
-      <c r="BN15" s="32"/>
-      <c r="BO15" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
-      </c>
-      <c r="BP15" s="31"/>
-      <c r="BQ15" s="32"/>
-      <c r="BR15" s="33" t="str">
-        <f t="shared" si="35"/>
-        <v>NA</v>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="BM15" s="31">
+        <v>2</v>
+      </c>
+      <c r="BN15" s="34">
+        <v>3.9930555555555552E-3</v>
+      </c>
+      <c r="BO15" s="33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="BP15" s="31">
+        <v>1</v>
+      </c>
+      <c r="BQ15" s="34">
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="BR15" s="33">
+        <f t="shared" si="41"/>
+        <v>2.2673611111111113E-2</v>
       </c>
       <c r="BS15" s="31"/>
-      <c r="BT15" s="34"/>
+      <c r="BT15" s="32"/>
       <c r="BU15" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BV15" s="31"/>
-      <c r="BW15" s="70"/>
-      <c r="BX15" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV15" s="31">
+        <v>1</v>
+      </c>
+      <c r="BW15" s="34">
+        <v>1.4675925925925926E-2</v>
+      </c>
+      <c r="BX15" s="33">
+        <f t="shared" si="43"/>
+        <v>1.068287037037037E-2</v>
+      </c>
+      <c r="BY15" s="31"/>
+      <c r="BZ15" s="70"/>
+      <c r="CA15" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY15" s="31"/>
-      <c r="BZ15" s="56"/>
-      <c r="CA15" s="33" t="str">
+      <c r="CB15" s="31"/>
+      <c r="CC15" s="56"/>
+      <c r="CD15" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
-      <c r="CB15" s="31"/>
-      <c r="CC15" s="70"/>
-      <c r="CD15" s="33" t="str">
+      <c r="CE15" s="31">
+        <v>1</v>
+      </c>
+      <c r="CF15" s="70">
+        <v>1.1284722222222222E-2</v>
+      </c>
+      <c r="CG15" s="33">
         <f t="shared" si="15"/>
-        <v>NA</v>
-      </c>
-      <c r="CE15" s="31"/>
-      <c r="CF15" s="70"/>
-      <c r="CG15" s="33" t="str">
+        <v>7.2916666666666668E-3</v>
+      </c>
+      <c r="CH15" s="31"/>
+      <c r="CI15" s="70"/>
+      <c r="CJ15" s="33" t="str">
         <f t="shared" si="16"/>
-        <v>NA</v>
-      </c>
-      <c r="CH15" s="31"/>
-      <c r="CI15" s="32"/>
-      <c r="CJ15" s="33" t="str">
-        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CK15" s="31"/>
       <c r="CL15" s="32"/>
       <c r="CM15" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN15" s="31"/>
       <c r="CO15" s="32"/>
       <c r="CP15" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ15" s="31"/>
       <c r="CR15" s="32"/>
       <c r="CS15" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT15" s="31"/>
       <c r="CU15" s="32"/>
       <c r="CV15" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW15" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW15" s="31"/>
+      <c r="CX15" s="32"/>
+      <c r="CY15" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ15" s="31">
+        <v>1</v>
+      </c>
+      <c r="DA15" s="34">
+        <v>1.6354166666666666E-2</v>
+      </c>
+      <c r="DB15" s="33">
+        <f t="shared" si="22"/>
+        <v>1.2361111111111111E-2</v>
+      </c>
+      <c r="DC15" s="31"/>
+      <c r="DD15" s="32"/>
+      <c r="DE15" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF15" s="31"/>
+      <c r="DG15" s="32"/>
+      <c r="DH15" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI15" s="31"/>
+      <c r="DJ15" s="32"/>
+      <c r="DK15" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL15" s="31"/>
+      <c r="DM15" s="32"/>
+      <c r="DN15" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO15" s="31"/>
+      <c r="DP15" s="32"/>
+      <c r="DQ15" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR15" s="35"/>
     </row>
-    <row r="16" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>149</v>
       </c>
@@ -4635,7 +5874,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>D3</v>
       </c>
       <c r="G16" s="5">
@@ -4671,7 +5910,7 @@
         <v>3</v>
       </c>
       <c r="Q16" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.3472222222222199E-2</v>
       </c>
       <c r="R16" s="6" t="s">
@@ -4687,49 +5926,65 @@
         <v>156</v>
       </c>
       <c r="V16" s="8"/>
-      <c r="W16" s="19"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
+      <c r="W16" s="19">
+        <v>1.7638888888888888E-2</v>
+      </c>
+      <c r="X16" s="20">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="Y16" s="20">
+        <v>5.6597222222222222E-3</v>
+      </c>
       <c r="Z16" s="20"/>
       <c r="AA16" s="20"/>
       <c r="AB16" s="20"/>
       <c r="AC16" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.1157407407407406E-2</v>
+      </c>
+      <c r="AD16" s="20">
+        <v>4.3981481481481484E-3</v>
+      </c>
       <c r="AE16" s="20"/>
       <c r="AF16" s="20">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG16" s="21"/>
-      <c r="AH16" s="21"/>
+        <f t="shared" si="32"/>
+        <v>3.6759259259259255E-2</v>
+      </c>
+      <c r="AG16" s="21">
+        <v>90</v>
+      </c>
+      <c r="AH16" s="21">
+        <v>100</v>
+      </c>
       <c r="AI16" s="22"/>
-      <c r="AJ16" s="29"/>
-      <c r="AK16" s="30"/>
+      <c r="AJ16" s="29">
+        <v>2</v>
+      </c>
+      <c r="AK16" s="30">
+        <v>2</v>
+      </c>
       <c r="AL16" s="31"/>
       <c r="AM16" s="34"/>
       <c r="AN16" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO16" s="31"/>
       <c r="AP16" s="34"/>
       <c r="AQ16" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR16" s="31"/>
       <c r="AS16" s="34"/>
       <c r="AT16" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU16" s="31"/>
       <c r="AV16" s="34"/>
       <c r="AW16" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX16" s="31"/>
@@ -4741,102 +5996,152 @@
       <c r="BA16" s="31"/>
       <c r="BB16" s="34"/>
       <c r="BC16" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD16" s="31"/>
       <c r="BE16" s="34"/>
       <c r="BF16" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG16" s="31"/>
       <c r="BH16" s="34"/>
-      <c r="BI16" s="56" t="str">
-        <f t="shared" si="32"/>
+      <c r="BI16" s="33" t="str">
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ16" s="31"/>
       <c r="BK16" s="34"/>
-      <c r="BL16" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BM16" s="31"/>
-      <c r="BN16" s="32"/>
-      <c r="BO16" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
+      <c r="BL16" s="56" t="str">
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="BM16" s="31">
+        <v>2</v>
+      </c>
+      <c r="BN16" s="34">
+        <v>5.8217592592592592E-3</v>
+      </c>
+      <c r="BO16" s="33">
+        <f t="shared" si="40"/>
+        <v>1.4236111111111107E-3</v>
       </c>
       <c r="BP16" s="31"/>
       <c r="BQ16" s="32"/>
       <c r="BR16" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS16" s="31"/>
-      <c r="BT16" s="56"/>
+      <c r="BT16" s="32"/>
       <c r="BU16" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BV16" s="31"/>
-      <c r="BW16" s="32"/>
-      <c r="BX16" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV16" s="31">
+        <v>1</v>
+      </c>
+      <c r="BW16" s="56">
+        <v>2.5717592592592594E-2</v>
+      </c>
+      <c r="BX16" s="33">
+        <f t="shared" si="43"/>
+        <v>2.1319444444444446E-2</v>
+      </c>
+      <c r="BY16" s="31"/>
+      <c r="BZ16" s="32"/>
+      <c r="CA16" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY16" s="31"/>
-      <c r="BZ16" s="56"/>
-      <c r="CA16" s="33" t="str">
+      <c r="CB16" s="31"/>
+      <c r="CC16" s="56"/>
+      <c r="CD16" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB16" s="31"/>
-      <c r="CC16" s="34"/>
-      <c r="CD16" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE16" s="31"/>
       <c r="CF16" s="34"/>
       <c r="CG16" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH16" s="31"/>
       <c r="CI16" s="34"/>
       <c r="CJ16" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK16" s="31"/>
       <c r="CL16" s="34"/>
       <c r="CM16" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN16" s="31"/>
       <c r="CO16" s="34"/>
       <c r="CP16" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ16" s="31"/>
       <c r="CR16" s="34"/>
       <c r="CS16" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT16" s="31"/>
       <c r="CU16" s="34"/>
       <c r="CV16" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW16" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW16" s="31"/>
+      <c r="CX16" s="34"/>
+      <c r="CY16" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ16" s="31"/>
+      <c r="DA16" s="34"/>
+      <c r="DB16" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC16" s="31"/>
+      <c r="DD16" s="34"/>
+      <c r="DE16" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF16" s="31"/>
+      <c r="DG16" s="34"/>
+      <c r="DH16" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI16" s="31"/>
+      <c r="DJ16" s="34"/>
+      <c r="DK16" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL16" s="31"/>
+      <c r="DM16" s="34"/>
+      <c r="DN16" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO16" s="31"/>
+      <c r="DP16" s="34"/>
+      <c r="DQ16" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR16" s="35"/>
     </row>
-    <row r="17" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
         <v>149</v>
       </c>
@@ -4853,7 +6158,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>E1</v>
       </c>
       <c r="G17" s="5">
@@ -4889,7 +6194,7 @@
         <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>6.6666666666666652E-2</v>
       </c>
       <c r="R17" s="6"/>
@@ -4903,49 +6208,65 @@
         <v>156</v>
       </c>
       <c r="V17" s="8"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
+      <c r="W17" s="19">
+        <v>1.511574074074074E-2</v>
+      </c>
+      <c r="X17" s="20">
+        <v>1.4861111111111111E-2</v>
+      </c>
+      <c r="Y17" s="20">
+        <v>1.3530092592592592E-2</v>
+      </c>
       <c r="Z17" s="20"/>
       <c r="AA17" s="20"/>
       <c r="AB17" s="20"/>
       <c r="AC17" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.3506944444444445E-2</v>
+      </c>
+      <c r="AD17" s="20">
+        <v>4.1087962962962962E-3</v>
+      </c>
       <c r="AE17" s="20"/>
       <c r="AF17" s="20">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
+        <f t="shared" si="32"/>
+        <v>3.9398148148148147E-2</v>
+      </c>
+      <c r="AG17" s="21">
+        <v>90</v>
+      </c>
+      <c r="AH17" s="21">
+        <v>95</v>
+      </c>
       <c r="AI17" s="22"/>
-      <c r="AJ17" s="29"/>
-      <c r="AK17" s="30"/>
+      <c r="AJ17" s="29">
+        <v>2</v>
+      </c>
+      <c r="AK17" s="30">
+        <v>2</v>
+      </c>
       <c r="AL17" s="31"/>
       <c r="AM17" s="34"/>
       <c r="AN17" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO17" s="31"/>
       <c r="AP17" s="34"/>
       <c r="AQ17" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR17" s="31"/>
       <c r="AS17" s="34"/>
       <c r="AT17" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU17" s="31"/>
       <c r="AV17" s="34"/>
       <c r="AW17" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX17" s="31"/>
@@ -4954,105 +6275,155 @@
         <f t="shared" si="5"/>
         <v>NA</v>
       </c>
-      <c r="BA17" s="31"/>
-      <c r="BB17" s="34"/>
-      <c r="BC17" s="33" t="str">
-        <f t="shared" si="30"/>
-        <v>NA</v>
+      <c r="BA17" s="31">
+        <v>1</v>
+      </c>
+      <c r="BB17" s="34">
+        <v>3.170138888888889E-2</v>
+      </c>
+      <c r="BC17" s="33">
+        <f t="shared" si="37"/>
+        <v>2.7592592592592592E-2</v>
       </c>
       <c r="BD17" s="31"/>
       <c r="BE17" s="34"/>
       <c r="BF17" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG17" s="31"/>
       <c r="BH17" s="34"/>
       <c r="BI17" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ17" s="31"/>
       <c r="BK17" s="34"/>
       <c r="BL17" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM17" s="31"/>
       <c r="BN17" s="34"/>
       <c r="BO17" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP17" s="31"/>
       <c r="BQ17" s="34"/>
       <c r="BR17" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS17" s="31"/>
-      <c r="BT17" s="32"/>
+      <c r="BT17" s="34"/>
       <c r="BU17" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV17" s="31"/>
       <c r="BW17" s="32"/>
       <c r="BX17" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BY17" s="31"/>
+      <c r="BZ17" s="32"/>
+      <c r="CA17" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY17" s="31"/>
-      <c r="BZ17" s="56"/>
-      <c r="CA17" s="33" t="str">
+      <c r="CB17" s="31"/>
+      <c r="CC17" s="56"/>
+      <c r="CD17" s="33" t="str">
         <f t="shared" si="14"/>
         <v>NA</v>
       </c>
-      <c r="CB17" s="31"/>
-      <c r="CC17" s="34"/>
-      <c r="CD17" s="33" t="str">
+      <c r="CE17" s="31">
+        <v>1</v>
+      </c>
+      <c r="CF17" s="34">
+        <v>3.1909722222222221E-2</v>
+      </c>
+      <c r="CG17" s="33">
         <f t="shared" si="15"/>
-        <v>NA</v>
-      </c>
-      <c r="CE17" s="31"/>
-      <c r="CF17" s="34"/>
-      <c r="CG17" s="33" t="str">
-        <f t="shared" si="16"/>
-        <v>NA</v>
+        <v>2.7800925925925923E-2</v>
       </c>
       <c r="CH17" s="31"/>
       <c r="CI17" s="34"/>
       <c r="CJ17" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK17" s="31"/>
       <c r="CL17" s="34"/>
       <c r="CM17" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN17" s="31"/>
       <c r="CO17" s="34"/>
       <c r="CP17" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ17" s="31"/>
       <c r="CR17" s="34"/>
       <c r="CS17" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT17" s="31"/>
       <c r="CU17" s="34"/>
       <c r="CV17" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW17" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW17" s="31"/>
+      <c r="CX17" s="34"/>
+      <c r="CY17" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ17" s="31"/>
+      <c r="DA17" s="34"/>
+      <c r="DB17" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC17" s="31"/>
+      <c r="DD17" s="34"/>
+      <c r="DE17" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF17" s="31"/>
+      <c r="DG17" s="34"/>
+      <c r="DH17" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI17" s="31"/>
+      <c r="DJ17" s="34"/>
+      <c r="DK17" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL17" s="31"/>
+      <c r="DM17" s="34"/>
+      <c r="DN17" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO17" s="31"/>
+      <c r="DP17" s="34"/>
+      <c r="DQ17" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR17" s="35"/>
     </row>
-    <row r="18" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>149</v>
       </c>
@@ -5069,7 +6440,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>E2</v>
       </c>
       <c r="G18" s="5">
@@ -5105,7 +6476,7 @@
         <v>3</v>
       </c>
       <c r="Q18" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.9722222222222177E-2</v>
       </c>
       <c r="R18" s="6"/>
@@ -5119,49 +6490,65 @@
         <v>156</v>
       </c>
       <c r="V18" s="8"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
+      <c r="W18" s="19">
+        <v>1.8935185185185187E-2</v>
+      </c>
+      <c r="X18" s="20">
+        <v>1.8298611111111113E-2</v>
+      </c>
+      <c r="Y18" s="20">
+        <v>1.193287037037037E-2</v>
+      </c>
       <c r="Z18" s="20"/>
       <c r="AA18" s="20"/>
       <c r="AB18" s="20"/>
       <c r="AC18" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD18" s="20"/>
+        <f t="shared" si="30"/>
+        <v>4.9166666666666671E-2</v>
+      </c>
+      <c r="AD18" s="20">
+        <v>3.9930555555555552E-3</v>
+      </c>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
+        <f t="shared" si="32"/>
+        <v>4.5173611111111116E-2</v>
+      </c>
+      <c r="AG18" s="21">
+        <v>80</v>
+      </c>
+      <c r="AH18" s="21">
+        <v>25</v>
+      </c>
       <c r="AI18" s="22"/>
-      <c r="AJ18" s="29"/>
-      <c r="AK18" s="30"/>
+      <c r="AJ18" s="29">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="30">
+        <v>2</v>
+      </c>
       <c r="AL18" s="31"/>
       <c r="AM18" s="34"/>
       <c r="AN18" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO18" s="31"/>
       <c r="AP18" s="34"/>
       <c r="AQ18" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR18" s="31"/>
       <c r="AS18" s="34"/>
       <c r="AT18" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU18" s="31"/>
       <c r="AV18" s="34"/>
       <c r="AW18" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX18" s="31"/>
@@ -5173,102 +6560,156 @@
       <c r="BA18" s="31"/>
       <c r="BB18" s="34"/>
       <c r="BC18" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD18" s="31"/>
       <c r="BE18" s="34"/>
       <c r="BF18" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG18" s="31"/>
       <c r="BH18" s="34"/>
       <c r="BI18" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ18" s="31"/>
       <c r="BK18" s="34"/>
       <c r="BL18" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BM18" s="31"/>
-      <c r="BN18" s="34"/>
-      <c r="BO18" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="BM18" s="31">
+        <v>2</v>
+      </c>
+      <c r="BN18" s="34">
+        <v>2.7083333333333334E-2</v>
+      </c>
+      <c r="BO18" s="33">
+        <f t="shared" si="40"/>
+        <v>2.3090277777777779E-2</v>
       </c>
       <c r="BP18" s="31"/>
       <c r="BQ18" s="34"/>
       <c r="BR18" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS18" s="31"/>
-      <c r="BT18" s="32"/>
+      <c r="BT18" s="34"/>
       <c r="BU18" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BV18" s="31"/>
-      <c r="BW18" s="32"/>
-      <c r="BX18" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV18" s="31">
+        <v>1</v>
+      </c>
+      <c r="BW18" s="34">
+        <v>1.1956018518518519E-2</v>
+      </c>
+      <c r="BX18" s="33">
+        <f t="shared" si="43"/>
+        <v>7.9629629629629634E-3</v>
+      </c>
+      <c r="BY18" s="31"/>
+      <c r="BZ18" s="32"/>
+      <c r="CA18" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY18" s="31"/>
-      <c r="BZ18" s="56"/>
-      <c r="CA18" s="33" t="str">
+      <c r="CB18" s="31"/>
+      <c r="CC18" s="56"/>
+      <c r="CD18" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB18" s="31"/>
-      <c r="CC18" s="34"/>
-      <c r="CD18" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE18" s="31"/>
       <c r="CF18" s="34"/>
       <c r="CG18" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH18" s="31"/>
       <c r="CI18" s="34"/>
       <c r="CJ18" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK18" s="31"/>
       <c r="CL18" s="34"/>
       <c r="CM18" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN18" s="31"/>
       <c r="CO18" s="34"/>
       <c r="CP18" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ18" s="31"/>
       <c r="CR18" s="34"/>
       <c r="CS18" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT18" s="31"/>
       <c r="CU18" s="34"/>
       <c r="CV18" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW18" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW18" s="31"/>
+      <c r="CX18" s="34"/>
+      <c r="CY18" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ18" s="31"/>
+      <c r="DA18" s="34"/>
+      <c r="DB18" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC18" s="31"/>
+      <c r="DD18" s="34"/>
+      <c r="DE18" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF18" s="31"/>
+      <c r="DG18" s="34"/>
+      <c r="DH18" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI18" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ18" s="34">
+        <v>1.3263888888888889E-2</v>
+      </c>
+      <c r="DK18" s="33">
+        <f t="shared" si="25"/>
+        <v>9.2708333333333341E-3</v>
+      </c>
+      <c r="DL18" s="31"/>
+      <c r="DM18" s="34"/>
+      <c r="DN18" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO18" s="31"/>
+      <c r="DP18" s="34"/>
+      <c r="DQ18" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR18" s="35"/>
     </row>
-    <row r="19" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>149</v>
       </c>
@@ -5285,7 +6726,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>E3</v>
       </c>
       <c r="G19" s="5">
@@ -5321,7 +6762,7 @@
         <v>2</v>
       </c>
       <c r="Q19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>5.4166666666666696E-2</v>
       </c>
       <c r="R19" s="6"/>
@@ -5335,49 +6776,63 @@
         <v>156</v>
       </c>
       <c r="V19" s="8"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="20"/>
+      <c r="W19" s="19">
+        <v>1.7858796296296296E-2</v>
+      </c>
+      <c r="X19" s="20">
+        <v>1.3564814814814814E-2</v>
+      </c>
       <c r="Y19" s="20"/>
       <c r="Z19" s="20"/>
       <c r="AA19" s="20"/>
       <c r="AB19" s="20"/>
       <c r="AC19" s="20">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AD19" s="20"/>
+        <f t="shared" si="30"/>
+        <v>3.142361111111111E-2</v>
+      </c>
+      <c r="AD19" s="20">
+        <v>3.8194444444444443E-3</v>
+      </c>
       <c r="AE19" s="20"/>
       <c r="AF19" s="20">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
+        <f t="shared" si="32"/>
+        <v>2.7604166666666666E-2</v>
+      </c>
+      <c r="AG19" s="21">
+        <v>70</v>
+      </c>
+      <c r="AH19" s="21">
+        <v>95</v>
+      </c>
       <c r="AI19" s="22"/>
-      <c r="AJ19" s="29"/>
-      <c r="AK19" s="30"/>
+      <c r="AJ19" s="29">
+        <v>3</v>
+      </c>
+      <c r="AK19" s="30">
+        <v>2</v>
+      </c>
       <c r="AL19" s="31"/>
       <c r="AM19" s="34"/>
       <c r="AN19" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO19" s="31"/>
       <c r="AP19" s="34"/>
       <c r="AQ19" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR19" s="31"/>
       <c r="AS19" s="34"/>
       <c r="AT19" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU19" s="31"/>
       <c r="AV19" s="34"/>
       <c r="AW19" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX19" s="31"/>
@@ -5389,102 +6844,156 @@
       <c r="BA19" s="31"/>
       <c r="BB19" s="34"/>
       <c r="BC19" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD19" s="31"/>
       <c r="BE19" s="34"/>
       <c r="BF19" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG19" s="31"/>
       <c r="BH19" s="34"/>
       <c r="BI19" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ19" s="31"/>
       <c r="BK19" s="34"/>
       <c r="BL19" s="33" t="str">
-        <f t="shared" si="33"/>
-        <v>NA</v>
-      </c>
-      <c r="BM19" s="31"/>
-      <c r="BN19" s="34"/>
-      <c r="BO19" s="33" t="str">
-        <f t="shared" si="34"/>
-        <v>NA</v>
+        <f t="shared" si="39"/>
+        <v>NA</v>
+      </c>
+      <c r="BM19" s="31">
+        <v>2</v>
+      </c>
+      <c r="BN19" s="34">
+        <v>6.6203703703703702E-3</v>
+      </c>
+      <c r="BO19" s="33">
+        <f t="shared" si="40"/>
+        <v>2.8009259259259259E-3</v>
       </c>
       <c r="BP19" s="31"/>
       <c r="BQ19" s="34"/>
       <c r="BR19" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS19" s="31"/>
-      <c r="BT19" s="32"/>
+      <c r="BT19" s="34"/>
       <c r="BU19" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v>NA</v>
-      </c>
-      <c r="BV19" s="31"/>
-      <c r="BW19" s="32"/>
-      <c r="BX19" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v>NA</v>
+      </c>
+      <c r="BV19" s="31">
+        <v>1</v>
+      </c>
+      <c r="BW19" s="34">
+        <v>8.5300925925925926E-3</v>
+      </c>
+      <c r="BX19" s="33">
+        <f t="shared" si="43"/>
+        <v>4.7106481481481478E-3</v>
+      </c>
+      <c r="BY19" s="31"/>
+      <c r="BZ19" s="32"/>
+      <c r="CA19" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY19" s="31"/>
-      <c r="BZ19" s="56"/>
-      <c r="CA19" s="33" t="str">
+      <c r="CB19" s="31"/>
+      <c r="CC19" s="56"/>
+      <c r="CD19" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB19" s="31"/>
-      <c r="CC19" s="34"/>
-      <c r="CD19" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE19" s="31"/>
       <c r="CF19" s="34"/>
       <c r="CG19" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH19" s="31"/>
       <c r="CI19" s="34"/>
       <c r="CJ19" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK19" s="31"/>
       <c r="CL19" s="34"/>
       <c r="CM19" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN19" s="31"/>
       <c r="CO19" s="34"/>
       <c r="CP19" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ19" s="31"/>
       <c r="CR19" s="34"/>
       <c r="CS19" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT19" s="31"/>
       <c r="CU19" s="34"/>
       <c r="CV19" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW19" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW19" s="31"/>
+      <c r="CX19" s="34"/>
+      <c r="CY19" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ19" s="31"/>
+      <c r="DA19" s="34"/>
+      <c r="DB19" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC19" s="31"/>
+      <c r="DD19" s="34"/>
+      <c r="DE19" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF19" s="31"/>
+      <c r="DG19" s="34"/>
+      <c r="DH19" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI19" s="31">
+        <v>1</v>
+      </c>
+      <c r="DJ19" s="34">
+        <v>3.8194444444444443E-3</v>
+      </c>
+      <c r="DK19" s="33">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="DL19" s="31"/>
+      <c r="DM19" s="34"/>
+      <c r="DN19" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO19" s="31"/>
+      <c r="DP19" s="34"/>
+      <c r="DQ19" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR19" s="35"/>
     </row>
-    <row r="20" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>149</v>
       </c>
@@ -5495,7 +7004,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="G20" s="5"/>
@@ -5515,7 +7024,7 @@
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R20" s="6"/>
@@ -5530,13 +7039,13 @@
       <c r="AA20" s="20"/>
       <c r="AB20" s="20"/>
       <c r="AC20" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD20" s="20"/>
       <c r="AE20" s="20"/>
       <c r="AF20" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AG20" s="21"/>
@@ -5547,25 +7056,25 @@
       <c r="AL20" s="31"/>
       <c r="AM20" s="34"/>
       <c r="AN20" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO20" s="31"/>
       <c r="AP20" s="34"/>
       <c r="AQ20" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR20" s="31"/>
       <c r="AS20" s="34"/>
       <c r="AT20" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU20" s="31"/>
       <c r="AV20" s="34"/>
       <c r="AW20" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX20" s="31"/>
@@ -5577,102 +7086,144 @@
       <c r="BA20" s="31"/>
       <c r="BB20" s="34"/>
       <c r="BC20" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD20" s="31"/>
       <c r="BE20" s="34"/>
       <c r="BF20" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG20" s="31"/>
       <c r="BH20" s="34"/>
       <c r="BI20" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ20" s="31"/>
       <c r="BK20" s="34"/>
       <c r="BL20" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM20" s="31"/>
       <c r="BN20" s="34"/>
       <c r="BO20" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP20" s="31"/>
       <c r="BQ20" s="34"/>
       <c r="BR20" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS20" s="31"/>
       <c r="BT20" s="34"/>
       <c r="BU20" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV20" s="31"/>
       <c r="BW20" s="34"/>
       <c r="BX20" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BY20" s="31"/>
+      <c r="BZ20" s="34"/>
+      <c r="CA20" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY20" s="31"/>
-      <c r="BZ20" s="56"/>
-      <c r="CA20" s="33" t="str">
+      <c r="CB20" s="31"/>
+      <c r="CC20" s="56"/>
+      <c r="CD20" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB20" s="31"/>
-      <c r="CC20" s="34"/>
-      <c r="CD20" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE20" s="31"/>
       <c r="CF20" s="34"/>
       <c r="CG20" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH20" s="31"/>
       <c r="CI20" s="34"/>
       <c r="CJ20" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK20" s="31"/>
       <c r="CL20" s="34"/>
       <c r="CM20" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN20" s="31"/>
       <c r="CO20" s="34"/>
       <c r="CP20" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ20" s="31"/>
       <c r="CR20" s="34"/>
       <c r="CS20" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>NA</v>
       </c>
       <c r="CT20" s="31"/>
       <c r="CU20" s="34"/>
       <c r="CV20" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW20" s="35"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW20" s="31"/>
+      <c r="CX20" s="34"/>
+      <c r="CY20" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ20" s="31"/>
+      <c r="DA20" s="34"/>
+      <c r="DB20" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC20" s="31"/>
+      <c r="DD20" s="34"/>
+      <c r="DE20" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF20" s="31"/>
+      <c r="DG20" s="34"/>
+      <c r="DH20" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI20" s="31"/>
+      <c r="DJ20" s="34"/>
+      <c r="DK20" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL20" s="31"/>
+      <c r="DM20" s="34"/>
+      <c r="DN20" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO20" s="31"/>
+      <c r="DP20" s="34"/>
+      <c r="DQ20" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR20" s="35"/>
     </row>
-    <row r="21" spans="1:101" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>149</v>
       </c>
@@ -5683,7 +7234,7 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="74" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="G21" s="5"/>
@@ -5703,7 +7254,7 @@
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R21" s="5"/>
@@ -5718,13 +7269,13 @@
       <c r="AA21" s="77"/>
       <c r="AB21" s="77"/>
       <c r="AC21" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD21" s="78"/>
       <c r="AE21" s="78"/>
       <c r="AF21" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AG21" s="21"/>
@@ -5735,25 +7286,25 @@
       <c r="AL21" s="31"/>
       <c r="AM21" s="32"/>
       <c r="AN21" s="33" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO21" s="31"/>
       <c r="AP21" s="32"/>
       <c r="AQ21" s="33" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR21" s="31"/>
       <c r="AS21" s="32"/>
       <c r="AT21" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU21" s="31"/>
       <c r="AV21" s="32"/>
       <c r="AW21" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX21" s="31"/>
@@ -5765,102 +7316,144 @@
       <c r="BA21" s="31"/>
       <c r="BB21" s="34"/>
       <c r="BC21" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD21" s="31"/>
       <c r="BE21" s="32"/>
       <c r="BF21" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG21" s="31"/>
       <c r="BH21" s="32"/>
       <c r="BI21" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ21" s="31"/>
-      <c r="BK21" s="56"/>
+      <c r="BK21" s="32"/>
       <c r="BL21" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM21" s="31"/>
-      <c r="BN21" s="32"/>
+      <c r="BN21" s="56"/>
       <c r="BO21" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP21" s="31"/>
       <c r="BQ21" s="32"/>
       <c r="BR21" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS21" s="31"/>
       <c r="BT21" s="32"/>
       <c r="BU21" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV21" s="31"/>
       <c r="BW21" s="32"/>
       <c r="BX21" s="33" t="str">
+        <f t="shared" si="43"/>
+        <v>NA</v>
+      </c>
+      <c r="BY21" s="31"/>
+      <c r="BZ21" s="32"/>
+      <c r="CA21" s="33" t="str">
         <f t="shared" si="13"/>
         <v>NA</v>
       </c>
-      <c r="BY21" s="31"/>
-      <c r="BZ21" s="34"/>
-      <c r="CA21" s="33" t="str">
+      <c r="CB21" s="31"/>
+      <c r="CC21" s="34"/>
+      <c r="CD21" s="33" t="str">
         <f t="shared" si="14"/>
-        <v>NA</v>
-      </c>
-      <c r="CB21" s="31"/>
-      <c r="CC21" s="32"/>
-      <c r="CD21" s="33" t="str">
-        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CE21" s="31"/>
       <c r="CF21" s="32"/>
       <c r="CG21" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH21" s="31"/>
       <c r="CI21" s="32"/>
       <c r="CJ21" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK21" s="31"/>
       <c r="CL21" s="32"/>
       <c r="CM21" s="33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN21" s="31"/>
       <c r="CO21" s="32"/>
       <c r="CP21" s="33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>NA</v>
       </c>
       <c r="CQ21" s="31"/>
       <c r="CR21" s="32"/>
       <c r="CS21" s="33" t="str">
+        <f t="shared" si="19"/>
+        <v>NA</v>
+      </c>
+      <c r="CT21" s="31"/>
+      <c r="CU21" s="32"/>
+      <c r="CV21" s="33" t="str">
         <f t="shared" si="20"/>
         <v>NA</v>
       </c>
-      <c r="CT21" s="31"/>
-      <c r="CU21" s="56"/>
-      <c r="CV21" s="33" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW21" s="35"/>
+      <c r="CW21" s="31"/>
+      <c r="CX21" s="32"/>
+      <c r="CY21" s="33" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ21" s="31"/>
+      <c r="DA21" s="32"/>
+      <c r="DB21" s="33" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC21" s="31"/>
+      <c r="DD21" s="56"/>
+      <c r="DE21" s="33" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF21" s="31"/>
+      <c r="DG21" s="56"/>
+      <c r="DH21" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI21" s="31"/>
+      <c r="DJ21" s="56"/>
+      <c r="DK21" s="33" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL21" s="31"/>
+      <c r="DM21" s="56"/>
+      <c r="DN21" s="33" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO21" s="31"/>
+      <c r="DP21" s="56"/>
+      <c r="DQ21" s="33" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR21" s="35"/>
     </row>
-    <row r="22" spans="1:101" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:122" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
         <v>149</v>
       </c>
@@ -5871,7 +7464,7 @@
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
       <c r="F22" s="75" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="G22" s="11"/>
@@ -5891,7 +7484,7 @@
       <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="R22" s="11"/>
@@ -5906,13 +7499,13 @@
       <c r="AA22" s="69"/>
       <c r="AB22" s="69"/>
       <c r="AC22" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD22" s="80"/>
       <c r="AE22" s="80"/>
       <c r="AF22" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AG22" s="24"/>
@@ -5923,25 +7516,25 @@
       <c r="AL22" s="38"/>
       <c r="AM22" s="40"/>
       <c r="AN22" s="41" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="33"/>
         <v>NA</v>
       </c>
       <c r="AO22" s="38"/>
       <c r="AP22" s="40"/>
       <c r="AQ22" s="41" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="34"/>
         <v>NA</v>
       </c>
       <c r="AR22" s="38"/>
       <c r="AS22" s="82"/>
       <c r="AT22" s="41" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="35"/>
         <v>NA</v>
       </c>
       <c r="AU22" s="38"/>
       <c r="AV22" s="82"/>
       <c r="AW22" s="41" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="36"/>
         <v>NA</v>
       </c>
       <c r="AX22" s="38"/>
@@ -5953,100 +7546,142 @@
       <c r="BA22" s="38"/>
       <c r="BB22" s="40"/>
       <c r="BC22" s="41" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="37"/>
         <v>NA</v>
       </c>
       <c r="BD22" s="38"/>
       <c r="BE22" s="82"/>
       <c r="BF22" s="41" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="7"/>
         <v>NA</v>
       </c>
       <c r="BG22" s="38"/>
       <c r="BH22" s="82"/>
       <c r="BI22" s="41" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>NA</v>
       </c>
       <c r="BJ22" s="38"/>
-      <c r="BK22" s="40"/>
+      <c r="BK22" s="82"/>
       <c r="BL22" s="41" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="39"/>
         <v>NA</v>
       </c>
       <c r="BM22" s="38"/>
-      <c r="BN22" s="82"/>
+      <c r="BN22" s="40"/>
       <c r="BO22" s="41" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="40"/>
         <v>NA</v>
       </c>
       <c r="BP22" s="38"/>
       <c r="BQ22" s="82"/>
       <c r="BR22" s="41" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="41"/>
         <v>NA</v>
       </c>
       <c r="BS22" s="38"/>
       <c r="BT22" s="82"/>
       <c r="BU22" s="41" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="42"/>
         <v>NA</v>
       </c>
       <c r="BV22" s="38"/>
       <c r="BW22" s="82"/>
       <c r="BX22" s="41" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>NA</v>
       </c>
       <c r="BY22" s="38"/>
       <c r="BZ22" s="82"/>
       <c r="CA22" s="41" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>NA</v>
       </c>
       <c r="CB22" s="38"/>
       <c r="CC22" s="82"/>
       <c r="CD22" s="41" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>NA</v>
       </c>
       <c r="CE22" s="38"/>
       <c r="CF22" s="82"/>
       <c r="CG22" s="41" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>NA</v>
       </c>
       <c r="CH22" s="38"/>
       <c r="CI22" s="82"/>
       <c r="CJ22" s="41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>NA</v>
       </c>
       <c r="CK22" s="38"/>
       <c r="CL22" s="82"/>
       <c r="CM22" s="41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>NA</v>
       </c>
       <c r="CN22" s="38"/>
       <c r="CO22" s="82"/>
       <c r="CP22" s="41" t="str">
+        <f t="shared" si="18"/>
+        <v>NA</v>
+      </c>
+      <c r="CQ22" s="38"/>
+      <c r="CR22" s="82"/>
+      <c r="CS22" s="41" t="str">
         <f t="shared" si="19"/>
-        <v>NA</v>
-      </c>
-      <c r="CQ22" s="38"/>
-      <c r="CR22" s="40"/>
-      <c r="CS22" s="41" t="str">
-        <f t="shared" si="20"/>
         <v>NA</v>
       </c>
       <c r="CT22" s="38"/>
       <c r="CU22" s="40"/>
       <c r="CV22" s="41" t="str">
-        <f t="shared" si="37"/>
-        <v>NA</v>
-      </c>
-      <c r="CW22" s="39"/>
+        <f t="shared" si="20"/>
+        <v>NA</v>
+      </c>
+      <c r="CW22" s="38"/>
+      <c r="CX22" s="40"/>
+      <c r="CY22" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v>NA</v>
+      </c>
+      <c r="CZ22" s="38"/>
+      <c r="DA22" s="40"/>
+      <c r="DB22" s="41" t="str">
+        <f t="shared" si="22"/>
+        <v>NA</v>
+      </c>
+      <c r="DC22" s="38"/>
+      <c r="DD22" s="40"/>
+      <c r="DE22" s="41" t="str">
+        <f t="shared" si="44"/>
+        <v>NA</v>
+      </c>
+      <c r="DF22" s="38"/>
+      <c r="DG22" s="40"/>
+      <c r="DH22" s="41" t="str">
+        <f t="shared" si="24"/>
+        <v>NA</v>
+      </c>
+      <c r="DI22" s="38"/>
+      <c r="DJ22" s="40"/>
+      <c r="DK22" s="41" t="str">
+        <f t="shared" si="25"/>
+        <v>NA</v>
+      </c>
+      <c r="DL22" s="38"/>
+      <c r="DM22" s="40"/>
+      <c r="DN22" s="41" t="str">
+        <f t="shared" si="26"/>
+        <v>NA</v>
+      </c>
+      <c r="DO22" s="38"/>
+      <c r="DP22" s="40"/>
+      <c r="DQ22" s="41" t="str">
+        <f t="shared" si="27"/>
+        <v>NA</v>
+      </c>
+      <c r="DR22" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/URUVS/Datasheets/URUV/09.2024/September_RecordingData.xlsx
+++ b/URUVS/Datasheets/URUV/09.2024/September_RecordingData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\swulfing\Documents\GitHub\TanakekeProject\URUVS\Datasheets\URUV\09.2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7076D1-57C1-41C7-B62E-34A1C2922067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897B5139-5BD5-4788-9B2D-C49CAFCB2582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-9405" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -494,9 +494,6 @@
     <t>28/09/2024</t>
   </si>
   <si>
-    <t>LATANGPEO</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -572,9 +569,6 @@
     <t>29/09/2024</t>
   </si>
   <si>
-    <t>TOMPOTANAH</t>
-  </si>
-  <si>
     <t>29_09_2024_0708_C5_D1_TMPL3</t>
   </si>
   <si>
@@ -666,6 +660,12 @@
   </si>
   <si>
     <t>T1_ULAR</t>
+  </si>
+  <si>
+    <t>LANTANGPEO</t>
+  </si>
+  <si>
+    <t>TOMPOTANA</t>
   </si>
 </sst>
 </file>
@@ -1304,8 +1304,7 @@
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.453125" customWidth="1"/>
-    <col min="3" max="5" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7265625" customWidth="1"/>
+    <col min="3" max="6" width="8.7265625" customWidth="1"/>
     <col min="7" max="22" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="23" max="29" width="8.7265625" style="1" customWidth="1"/>
     <col min="30" max="36" width="8.7265625" customWidth="1"/>
@@ -1498,13 +1497,13 @@
         <v>38</v>
       </c>
       <c r="BD1" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="BE1" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="BF1" s="59" t="s">
         <v>203</v>
-      </c>
-      <c r="BE1" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="BF1" s="59" t="s">
-        <v>205</v>
       </c>
       <c r="BG1" s="81" t="s">
         <v>45</v>
@@ -1633,22 +1632,22 @@
         <v>143</v>
       </c>
       <c r="CW1" s="81" t="s">
+        <v>192</v>
+      </c>
+      <c r="CX1" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="CY1" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="CX1" s="27" t="s">
+      <c r="CZ1" s="81" t="s">
         <v>195</v>
       </c>
-      <c r="CY1" s="59" t="s">
+      <c r="DA1" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="CZ1" s="81" t="s">
+      <c r="DB1" s="59" t="s">
         <v>197</v>
-      </c>
-      <c r="DA1" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="DB1" s="59" t="s">
-        <v>199</v>
       </c>
       <c r="DC1" s="81" t="s">
         <v>12</v>
@@ -1660,40 +1659,40 @@
         <v>33</v>
       </c>
       <c r="DF1" s="81" t="s">
+        <v>186</v>
+      </c>
+      <c r="DG1" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="DH1" s="59" t="s">
         <v>188</v>
       </c>
-      <c r="DG1" s="27" t="s">
+      <c r="DI1" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="DH1" s="59" t="s">
+      <c r="DJ1" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="DI1" s="81" t="s">
+      <c r="DK1" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="DJ1" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="DK1" s="59" t="s">
-        <v>193</v>
-      </c>
       <c r="DL1" s="81" t="s">
+        <v>198</v>
+      </c>
+      <c r="DM1" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="DN1" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="DM1" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="DN1" s="59" t="s">
-        <v>202</v>
-      </c>
       <c r="DO1" s="81" t="s">
+        <v>204</v>
+      </c>
+      <c r="DP1" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="DQ1" s="59" t="s">
         <v>206</v>
-      </c>
-      <c r="DP1" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="DQ1" s="59" t="s">
-        <v>208</v>
       </c>
       <c r="DR1" s="28" t="s">
         <v>31</v>
@@ -1707,10 +1706,10 @@
         <v>150</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="E2" s="5">
         <v>5</v>
@@ -1746,7 +1745,7 @@
         <v>56</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P2" s="5">
         <v>3</v>
@@ -1756,16 +1755,16 @@
         <v>0.1020833333333333</v>
       </c>
       <c r="R2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="T2" s="5">
         <v>0.32</v>
       </c>
       <c r="U2" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V2" s="8"/>
       <c r="W2" s="19">
@@ -2003,10 +2002,10 @@
         <v>150</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="E3" s="5">
         <v>6</v>
@@ -2019,7 +2018,7 @@
         <v>2</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I3" s="6">
         <v>0.2638888888888889</v>
@@ -2042,7 +2041,7 @@
         <v>33</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="P3" s="5">
         <v>4</v>
@@ -2052,16 +2051,16 @@
         <v>0.10069444444444442</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T3" s="5">
         <v>0.35</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V3" s="8"/>
       <c r="W3" s="19">
@@ -2105,11 +2104,15 @@
       <c r="AK3" s="30">
         <v>7</v>
       </c>
-      <c r="AL3" s="31"/>
-      <c r="AM3" s="34"/>
-      <c r="AN3" s="33" t="str">
+      <c r="AL3" s="31">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="34">
+        <v>1.1585648148148149E-2</v>
+      </c>
+      <c r="AN3" s="33">
         <f t="shared" si="1"/>
-        <v>NA</v>
+        <v>7.2569444444444452E-3</v>
       </c>
       <c r="AO3" s="31"/>
       <c r="AP3" s="32"/>
@@ -2311,10 +2314,10 @@
         <v>150</v>
       </c>
       <c r="C4" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="E4" s="5">
         <v>4</v>
@@ -2350,7 +2353,7 @@
         <v>60</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P4" s="5">
         <v>3</v>
@@ -2360,16 +2363,16 @@
         <v>9.4444444444444442E-2</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T4" s="5">
         <v>0.35</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V4" s="8"/>
       <c r="W4" s="19">
@@ -2607,10 +2610,10 @@
         <v>150</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E5" s="5">
         <v>4</v>
@@ -2646,7 +2649,7 @@
         <v>36</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P5" s="5">
         <v>3</v>
@@ -2656,16 +2659,16 @@
         <v>5.2083333333333315E-2</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T5" s="5">
         <v>0.35</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V5" s="8"/>
       <c r="W5" s="19">
@@ -2903,10 +2906,10 @@
         <v>150</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="5">
         <v>5</v>
@@ -2942,7 +2945,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P6" s="5">
         <v>3</v>
@@ -2952,16 +2955,16 @@
         <v>8.4027777777777812E-2</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T6" s="5">
         <v>0.36</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V6" s="8"/>
       <c r="W6" s="19">
@@ -3199,10 +3202,10 @@
         <v>150</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="5">
         <v>6</v>
@@ -3238,7 +3241,7 @@
         <v>30</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P7" s="5">
         <v>3</v>
@@ -3248,16 +3251,16 @@
         <v>5.2777777777777812E-2</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T7" s="5">
         <v>0.37</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V7" s="8"/>
       <c r="W7" s="19">
@@ -3491,10 +3494,10 @@
         <v>150</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="5">
         <v>4</v>
@@ -3530,7 +3533,7 @@
         <v>20</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P8" s="5">
         <v>4</v>
@@ -3540,16 +3543,16 @@
         <v>7.0138888888888917E-2</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T8" s="5">
         <v>0.33</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V8" s="8"/>
       <c r="W8" s="19">
@@ -3789,10 +3792,10 @@
         <v>150</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
@@ -3828,7 +3831,7 @@
         <v>28</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P9" s="5">
         <v>2</v>
@@ -3838,16 +3841,16 @@
         <v>5.2777777777777812E-2</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T9" s="5">
         <v>0.37</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V9" s="8"/>
       <c r="W9" s="19">
@@ -4085,10 +4088,10 @@
         <v>150</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="5">
         <v>6</v>
@@ -4124,7 +4127,7 @@
         <v>25</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P10" s="5">
         <v>3</v>
@@ -4134,16 +4137,16 @@
         <v>7.0833333333333359E-2</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T10" s="5">
         <v>0.33</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="V10" s="8"/>
       <c r="W10" s="19">
@@ -4384,13 +4387,13 @@
         <v>149</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E11" s="5">
         <v>3</v>
@@ -4426,7 +4429,7 @@
         <v>52</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="P11" s="5">
         <v>3</v>
@@ -4436,16 +4439,16 @@
         <v>9.7916666666666652E-2</v>
       </c>
       <c r="R11" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S11" s="5" t="s">
         <v>154</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="T11" s="5">
         <v>0.25</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V11" s="8"/>
       <c r="W11" s="19">
@@ -4672,13 +4675,13 @@
         <v>149</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E12" s="5">
         <v>1</v>
@@ -4714,7 +4717,7 @@
         <v>50</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P12" s="5">
         <v>3</v>
@@ -4724,16 +4727,16 @@
         <v>9.7222222222222265E-2</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T12" s="5">
         <v>0.25</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V12" s="8"/>
       <c r="W12" s="19">
@@ -4964,13 +4967,13 @@
         <v>149</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E13" s="5">
         <v>2</v>
@@ -5006,7 +5009,7 @@
         <v>54</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P13" s="5">
         <v>3</v>
@@ -5016,16 +5019,16 @@
         <v>8.7500000000000022E-2</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T13" s="5">
         <v>0.27</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V13" s="8"/>
       <c r="W13" s="19">
@@ -5260,13 +5263,13 @@
         <v>149</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E14" s="5">
         <v>1</v>
@@ -5279,7 +5282,7 @@
         <v>4</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I14" s="6">
         <v>0.31458333333333333</v>
@@ -5302,7 +5305,7 @@
         <v>51</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P14" s="5">
         <v>5</v>
@@ -5312,16 +5315,16 @@
         <v>7.1527777777777801E-2</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T14" s="5">
         <v>0.27</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V14" s="8"/>
       <c r="W14" s="19">
@@ -5562,13 +5565,13 @@
         <v>149</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E15" s="5">
         <v>2</v>
@@ -5604,7 +5607,7 @@
         <v>40</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P15" s="5">
         <v>4</v>
@@ -5614,16 +5617,16 @@
         <v>6.0416666666666619E-2</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T15" s="5">
         <v>0.27</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V15" s="8"/>
       <c r="W15" s="19">
@@ -5862,13 +5865,13 @@
         <v>149</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="5">
         <v>3</v>
@@ -5904,7 +5907,7 @@
         <v>49</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P16" s="5">
         <v>3</v>
@@ -5914,16 +5917,16 @@
         <v>5.3472222222222199E-2</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T16" s="5">
         <v>0.28000000000000003</v>
       </c>
       <c r="U16" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V16" s="8"/>
       <c r="W16" s="19">
@@ -6146,13 +6149,13 @@
         <v>149</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E17" s="5">
         <v>1</v>
@@ -6165,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I17" s="6">
         <v>0.36319444444444443</v>
@@ -6188,7 +6191,7 @@
         <v>51</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P17" s="5">
         <v>3</v>
@@ -6199,13 +6202,13 @@
       </c>
       <c r="R17" s="6"/>
       <c r="S17" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T17" s="5">
         <v>0.18</v>
       </c>
       <c r="U17" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V17" s="8"/>
       <c r="W17" s="19">
@@ -6428,13 +6431,13 @@
         <v>149</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E18" s="5">
         <v>2</v>
@@ -6470,7 +6473,7 @@
         <v>60</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P18" s="5">
         <v>3</v>
@@ -6481,13 +6484,13 @@
       </c>
       <c r="R18" s="6"/>
       <c r="S18" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T18" s="5">
         <v>0.19</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V18" s="8"/>
       <c r="W18" s="19">
@@ -6714,13 +6717,13 @@
         <v>149</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E19" s="5">
         <v>3</v>
@@ -6756,7 +6759,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P19" s="5">
         <v>2</v>
@@ -6767,13 +6770,13 @@
       </c>
       <c r="R19" s="6"/>
       <c r="S19" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T19" s="5">
         <v>0.19</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V19" s="8"/>
       <c r="W19" s="19">
@@ -6998,7 +7001,7 @@
         <v>149</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="5"/>
@@ -7228,7 +7231,7 @@
         <v>149</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="5"/>
@@ -7458,7 +7461,7 @@
         <v>149</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
